--- a/sports_data.xlsx
+++ b/sports_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L83"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,21 +493,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fehérvár FC</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>ST Johnstone</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.35</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -527,33 +527,33 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>2.35</v>
+        <v>7.05</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Flora Tallinn</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -564,42 +564,42 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="J3" t="n">
         <v>100</v>
       </c>
       <c r="K3" t="n">
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Estrella</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dakota</t>
+          <t>Enppi</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.25</v>
+        <v>3.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -631,25 +631,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Coventry City U21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sheffield United U21</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.4</v>
+        <v>3.74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -659,43 +659,43 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>100</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Amazulu</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.72</v>
+        <v>5.75</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -705,10 +705,10 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -717,27 +717,27 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Persipal</t>
+          <t>Flint Mountain</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Persiba Balikpapan</t>
+          <t>Llandudno</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.65</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -769,47 +769,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vicenza Virtus</t>
+          <t>Bodo/Glimt</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.75</v>
+        <v>1.27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>85.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>85.2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14.8</v>
       </c>
       <c r="I8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>48.1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -820,62 +820,62 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Damac</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Al-Ahli Jeddah</t>
+          <t>FC Eindhoven</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9.4</v>
+        <v>1.38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>100</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>100</v>
+        <v>51.1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>America de Cali</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jaguares</t>
+          <t>Spanish Town Police</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -883,91 +883,91 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>85.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>85.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>10.7</v>
       </c>
       <c r="J10" t="n">
-        <v>51.1</v>
+        <v>39.3</v>
       </c>
       <c r="K10" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="L10" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt W</t>
+          <t>South Melbourne</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SC Freiburg W</t>
+          <t>Tahiti United</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>84</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>25.9</v>
+        <v>7.1</v>
       </c>
       <c r="I11" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="J11" t="n">
-        <v>84</v>
+        <v>39.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="L11" t="n">
-        <v>81</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Fenerbahçe</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.22</v>
+        <v>4.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -975,45 +975,45 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>82.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G12" t="n">
-        <v>82.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="H12" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10.7</v>
+        <v>20</v>
       </c>
       <c r="J12" t="n">
-        <v>39.3</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
-        <v>1.03</v>
+        <v>3.32</v>
       </c>
       <c r="L12" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kazma</t>
+          <t>Inter San Carlos</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Al Qadsia</t>
+          <t>AD Cofutpa</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.18</v>
+        <v>1.44</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1021,45 +1021,45 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>42.9</v>
+        <v>44.1</v>
       </c>
       <c r="H13" t="n">
-        <v>28.6</v>
+        <v>13.6</v>
       </c>
       <c r="I13" t="n">
-        <v>28.6</v>
+        <v>42.4</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K13" t="n">
-        <v>1.35</v>
+        <v>0.64</v>
       </c>
       <c r="L13" t="n">
-        <v>21</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Etar Veliko Tarnovo</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1091,21 +1091,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gais</t>
+          <t>Vardar Skopje</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Landskrona BoIS</t>
+          <t>Ohrid</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1113,229 +1113,229 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="G15" t="n">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="H15" t="n">
-        <v>11.8</v>
+        <v>13.3</v>
       </c>
       <c r="I15" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>58.8</v>
+        <v>56.7</v>
       </c>
       <c r="K15" t="n">
         <v>0.88</v>
       </c>
       <c r="L15" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Club Brugge KV</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>76.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>76.2</v>
+        <v>62.2</v>
       </c>
       <c r="H16" t="n">
-        <v>9.5</v>
+        <v>24.4</v>
       </c>
       <c r="I16" t="n">
-        <v>14.3</v>
+        <v>13.3</v>
       </c>
       <c r="J16" t="n">
-        <v>52.4</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="L16" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jong Ajax</t>
+          <t>Inter Kashi</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.49</v>
+        <v>4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G17" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="J17" t="n">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Matagalpa</t>
+          <t>Farense U23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Real Estelí</t>
+          <t>União Leiria U23</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>75</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>37.5</v>
+        <v>17.6</v>
       </c>
       <c r="I18" t="n">
-        <v>37.5</v>
+        <v>9.4</v>
       </c>
       <c r="J18" t="n">
-        <v>75</v>
+        <v>50.6</v>
       </c>
       <c r="K18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Qarabag</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.34</v>
+        <v>1.16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>75</v>
+        <v>72.2</v>
       </c>
       <c r="G19" t="n">
-        <v>33.3</v>
+        <v>72.2</v>
       </c>
       <c r="H19" t="n">
         <v>16.7</v>
       </c>
       <c r="I19" t="n">
-        <v>50</v>
+        <v>11.1</v>
       </c>
       <c r="J19" t="n">
-        <v>75</v>
+        <v>72.2</v>
       </c>
       <c r="K19" t="n">
-        <v>1.12</v>
+        <v>0.83</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Maidenhead</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chennaiyin</t>
+          <t>Salisbury</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1343,45 +1343,45 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>74.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G20" t="n">
-        <v>74.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>17.3</v>
       </c>
       <c r="I20" t="n">
-        <v>16.3</v>
+        <v>11.5</v>
       </c>
       <c r="J20" t="n">
-        <v>60.5</v>
+        <v>59.6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.93</v>
+        <v>1.03</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion U21</t>
+          <t>Swansea</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers U21</t>
+          <t>Preston</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1389,25 +1389,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>72.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="G21" t="n">
-        <v>72.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="H21" t="n">
-        <v>17.6</v>
+        <v>25</v>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>5</v>
       </c>
       <c r="J21" t="n">
-        <v>50.6</v>
+        <v>46.7</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="L21" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1418,62 +1418,62 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Barwell</t>
+          <t>Stirling Albion</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Halesowen Town</t>
+          <t>Annan Athletic</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>72.7</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="H22" t="n">
-        <v>27.3</v>
+        <v>60</v>
       </c>
       <c r="I22" t="n">
-        <v>72.7</v>
+        <v>17.1</v>
       </c>
       <c r="J22" t="n">
-        <v>54.5</v>
+        <v>25.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="L22" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Spennymoor Town</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Chorley</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3.78</v>
+        <v>2.75</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1481,45 +1481,45 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>38.1</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
+        <v>57.1</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>42.9</v>
       </c>
       <c r="K23" t="n">
-        <v>0.75</v>
+        <v>1.05</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Crewe Alexandra U21</t>
+          <t>Leamington</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peterborough United U21</t>
+          <t>Merthyr Town</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1530,19 +1530,19 @@
         <v>57.1</v>
       </c>
       <c r="G24" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>57.1</v>
       </c>
       <c r="I24" t="n">
-        <v>14.3</v>
+        <v>42.9</v>
       </c>
       <c r="J24" t="n">
-        <v>85.7</v>
+        <v>28.6</v>
       </c>
       <c r="K24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>7</v>
@@ -1551,21 +1551,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Monsoon</t>
+          <t>Curzon Ashton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avenida</t>
+          <t>Darlington 1883</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.36</v>
+        <v>2.95</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1573,45 +1573,45 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>48.9</v>
+        <v>56.8</v>
       </c>
       <c r="G25" t="n">
-        <v>26.7</v>
+        <v>16.2</v>
       </c>
       <c r="H25" t="n">
-        <v>48.9</v>
+        <v>56.8</v>
       </c>
       <c r="I25" t="n">
-        <v>24.4</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>42.2</v>
+        <v>35.1</v>
       </c>
       <c r="K25" t="n">
-        <v>0.63</v>
+        <v>0.48</v>
       </c>
       <c r="L25" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Obolon'-Brovar</t>
+          <t>Ipswich</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.38</v>
+        <v>3.24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1619,45 +1619,45 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>48.9</v>
+        <v>52</v>
       </c>
       <c r="G26" t="n">
-        <v>26.7</v>
+        <v>16</v>
       </c>
       <c r="H26" t="n">
-        <v>48.9</v>
+        <v>52</v>
       </c>
       <c r="I26" t="n">
-        <v>24.4</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>42.2</v>
+        <v>40</v>
       </c>
       <c r="K26" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="L26" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cucuta</t>
+          <t>FC Halifax Town</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Deportes Tolima</t>
+          <t>Rochdale</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.45</v>
+        <v>4.25</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1665,45 +1665,45 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>41.5</v>
+        <v>50</v>
       </c>
       <c r="G27" t="n">
-        <v>43.9</v>
+        <v>50</v>
       </c>
       <c r="H27" t="n">
-        <v>41.5</v>
+        <v>50</v>
       </c>
       <c r="I27" t="n">
-        <v>14.6</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>36.6</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>1.08</v>
+        <v>2.12</v>
       </c>
       <c r="L27" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Accrington ST</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5.85</v>
+        <v>3.56</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1711,13 +1711,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1726,30 +1726,30 @@
         <v>40</v>
       </c>
       <c r="K28" t="n">
-        <v>3.51</v>
+        <v>1.78</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MTK Budapest</t>
+          <t>Dover</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ferencvarosi TC</t>
+          <t>AFC Hornchurch</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.85</v>
+        <v>3.4</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1757,45 +1757,45 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G29" t="n">
-        <v>60</v>
+        <v>33.3</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J29" t="n">
-        <v>60</v>
+        <v>16.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.91</v>
+        <v>1.15</v>
       </c>
       <c r="L29" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Union Magdalena</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Deportivo La Guaira</t>
+          <t>Tigres FC</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4.15</v>
+        <v>1.47</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1803,275 +1803,275 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>25</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L30" t="n">
         <v>20</v>
-      </c>
-      <c r="J30" t="n">
-        <v>40</v>
-      </c>
-      <c r="K30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UCV Moquegua</t>
+          <t>Bath City</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Deportivo Garcilaso</t>
+          <t>Weston-super-Mare</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>3.04</v>
+        <v>2.71</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G31" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
       <c r="H31" t="n">
-        <v>30.8</v>
+        <v>50</v>
       </c>
       <c r="I31" t="n">
-        <v>15.4</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>53.8</v>
+        <v>50</v>
       </c>
       <c r="K31" t="n">
-        <v>1.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Academia Anzoátegui</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida FC</t>
+          <t>Nam Dinh</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.33</v>
+        <v>2.39</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>48.9</v>
       </c>
       <c r="G32" t="n">
-        <v>65.7</v>
+        <v>27.7</v>
       </c>
       <c r="H32" t="n">
-        <v>11.4</v>
+        <v>48.9</v>
       </c>
       <c r="I32" t="n">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
       <c r="J32" t="n">
-        <v>37.1</v>
+        <v>42.6</v>
       </c>
       <c r="K32" t="n">
-        <v>1.54</v>
+        <v>0.65</v>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jong AZ</t>
+          <t>Hanwell Town</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Plymouth Parkway</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.19</v>
+        <v>1.74</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>44.8</v>
       </c>
       <c r="G33" t="n">
-        <v>66.2</v>
+        <v>40.3</v>
       </c>
       <c r="H33" t="n">
-        <v>22.1</v>
+        <v>44.8</v>
       </c>
       <c r="I33" t="n">
-        <v>11.8</v>
+        <v>14.9</v>
       </c>
       <c r="J33" t="n">
-        <v>69.09999999999999</v>
+        <v>31.3</v>
       </c>
       <c r="K33" t="n">
-        <v>1.42</v>
+        <v>0.71</v>
       </c>
       <c r="L33" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>El Gouna FC</t>
+          <t>Bayern München II</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>El Mokawloon</t>
+          <t>SpVgg Unterhaching</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.53</v>
+        <v>2.99</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>42.9</v>
       </c>
       <c r="G34" t="n">
-        <v>55.2</v>
+        <v>38.1</v>
       </c>
       <c r="H34" t="n">
-        <v>27.6</v>
+        <v>42.9</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>48.3</v>
+        <v>38.1</v>
       </c>
       <c r="K34" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="L34" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Eastbourne Borough</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bali United</t>
+          <t>Dorking Wanderers</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.18</v>
+        <v>3.88</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G35" t="n">
-        <v>65.09999999999999</v>
+        <v>60</v>
       </c>
       <c r="H35" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="I35" t="n">
-        <v>20.9</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>44.2</v>
+        <v>40</v>
       </c>
       <c r="K35" t="n">
-        <v>1.4</v>
+        <v>2.31</v>
       </c>
       <c r="L35" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UAI Urquiza</t>
+          <t>Concordia</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Deportivo Camioneros</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.43</v>
+        <v>3.62</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2082,42 +2082,42 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>54.2</v>
+        <v>60</v>
       </c>
       <c r="H36" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="I36" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="J36" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="K36" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="L36" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Eintracht Frankf U19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Sporting CP U19</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2.42</v>
+        <v>3.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2128,42 +2128,42 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>54.2</v>
+        <v>60</v>
       </c>
       <c r="H37" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="I37" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>41.7</v>
+        <v>50</v>
       </c>
       <c r="K37" t="n">
-        <v>1.33</v>
+        <v>2.19</v>
       </c>
       <c r="L37" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2174,42 +2174,42 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>35.7</v>
+        <v>68</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I38" t="n">
-        <v>64.3</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>57.1</v>
+        <v>68</v>
       </c>
       <c r="K38" t="n">
-        <v>1.2</v>
+        <v>2.14</v>
       </c>
       <c r="L38" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sampaio Corrêa RJ</t>
+          <t>Masr</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nova Iguaçu</t>
+          <t>Zamalek SC</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.5</v>
+        <v>3.42</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2220,42 +2220,42 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>45.2</v>
+        <v>53.8</v>
       </c>
       <c r="H39" t="n">
-        <v>32.3</v>
+        <v>30.8</v>
       </c>
       <c r="I39" t="n">
-        <v>22.6</v>
+        <v>15.4</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="K39" t="n">
-        <v>1.15</v>
+        <v>1.86</v>
       </c>
       <c r="L39" t="n">
-        <v>62</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Javor</t>
+          <t>Scunthorpe</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>York</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1.85</v>
+        <v>3.32</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2266,42 +2266,42 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>60.6</v>
+        <v>53.8</v>
       </c>
       <c r="H40" t="n">
-        <v>18.2</v>
+        <v>23.1</v>
       </c>
       <c r="I40" t="n">
-        <v>21.2</v>
+        <v>23.1</v>
       </c>
       <c r="J40" t="n">
-        <v>60.6</v>
+        <v>61.5</v>
       </c>
       <c r="K40" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="L40" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Drenica Skënderaj</t>
+          <t>Oxford City</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prishtina e Re</t>
+          <t>AFC Telford United</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1.74</v>
+        <v>3.36</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2312,42 +2312,42 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>63.6</v>
+        <v>53.8</v>
       </c>
       <c r="H41" t="n">
-        <v>13.6</v>
+        <v>23.1</v>
       </c>
       <c r="I41" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="J41" t="n">
-        <v>59.1</v>
+        <v>61.5</v>
       </c>
       <c r="K41" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Dulwich Hamlet</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Chatham Town</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1.95</v>
+        <v>3.22</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2358,42 +2358,42 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>56.3</v>
+        <v>47.6</v>
       </c>
       <c r="H42" t="n">
-        <v>17.2</v>
+        <v>9.5</v>
       </c>
       <c r="I42" t="n">
-        <v>26.4</v>
+        <v>42.9</v>
       </c>
       <c r="J42" t="n">
-        <v>55.2</v>
+        <v>42.9</v>
       </c>
       <c r="K42" t="n">
-        <v>1.1</v>
+        <v>1.55</v>
       </c>
       <c r="L42" t="n">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Northampton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.93</v>
+        <v>2.33</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2404,42 +2404,42 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>56.3</v>
+        <v>65.7</v>
       </c>
       <c r="H43" t="n">
-        <v>17.2</v>
+        <v>11.4</v>
       </c>
       <c r="I43" t="n">
-        <v>26.4</v>
+        <v>22.9</v>
       </c>
       <c r="J43" t="n">
-        <v>55.2</v>
+        <v>37.1</v>
       </c>
       <c r="K43" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="L43" t="n">
-        <v>87</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kudrivka</t>
+          <t>Alfreton Town</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Zorya Luhansk</t>
+          <t>Scarborough Athletic</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.65</v>
+        <v>2.54</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2450,42 +2450,42 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>29.4</v>
+        <v>56.7</v>
       </c>
       <c r="H44" t="n">
-        <v>23.5</v>
+        <v>26.7</v>
       </c>
       <c r="I44" t="n">
-        <v>47.1</v>
+        <v>16.7</v>
       </c>
       <c r="J44" t="n">
-        <v>52.9</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>1.07</v>
+        <v>1.45</v>
       </c>
       <c r="L44" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Burnley U21</t>
+          <t>Ayr Utd</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derby County U21</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.12</v>
+        <v>2.58</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2496,22 +2496,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>47.1</v>
+        <v>56.7</v>
       </c>
       <c r="H45" t="n">
-        <v>29.4</v>
+        <v>26.7</v>
       </c>
       <c r="I45" t="n">
-        <v>23.5</v>
+        <v>16.7</v>
       </c>
       <c r="J45" t="n">
-        <v>45.1</v>
+        <v>50</v>
       </c>
       <c r="K45" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="L45" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trefelin</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Forli</t>
+          <t>Cambrian &amp; Clydach</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.67</v>
+        <v>2.74</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2542,42 +2542,42 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>60.9</v>
+        <v>52.4</v>
       </c>
       <c r="H46" t="n">
-        <v>30.4</v>
+        <v>38.1</v>
       </c>
       <c r="I46" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="J46" t="n">
-        <v>39.1</v>
+        <v>38.1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>1.44</v>
       </c>
       <c r="L46" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Luton</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.52</v>
+        <v>2.15</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2588,42 +2588,42 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>64</v>
+        <v>66.2</v>
       </c>
       <c r="H47" t="n">
-        <v>16</v>
+        <v>22.1</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>11.8</v>
       </c>
       <c r="J47" t="n">
-        <v>52</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>0.99</v>
+        <v>1.42</v>
       </c>
       <c r="L47" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>San Carlos</t>
+          <t>Charlton Athletic U21</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CS Herediano</t>
+          <t>Swansea City U21</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2634,42 +2634,42 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>34.5</v>
+        <v>66.2</v>
       </c>
       <c r="H48" t="n">
-        <v>31</v>
+        <v>22.1</v>
       </c>
       <c r="I48" t="n">
-        <v>34.5</v>
+        <v>11.8</v>
       </c>
       <c r="J48" t="n">
-        <v>62.1</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>0.98</v>
+        <v>1.42</v>
       </c>
       <c r="L48" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Reading U21</t>
+          <t>Bristol City U21</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Arsenal U21</t>
+          <t>Queens Park Rangers U21</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.84</v>
+        <v>2.23</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2680,42 +2680,42 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>34.5</v>
+        <v>59.7</v>
       </c>
       <c r="H49" t="n">
-        <v>31</v>
+        <v>29.2</v>
       </c>
       <c r="I49" t="n">
-        <v>34.5</v>
+        <v>11.1</v>
       </c>
       <c r="J49" t="n">
-        <v>62.1</v>
+        <v>50</v>
       </c>
       <c r="K49" t="n">
-        <v>0.98</v>
+        <v>1.34</v>
       </c>
       <c r="L49" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Tamworth</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Girona</t>
+          <t>Altrincham</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2726,42 +2726,42 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>38.9</v>
+        <v>57.6</v>
       </c>
       <c r="H50" t="n">
-        <v>16.7</v>
+        <v>18.2</v>
       </c>
       <c r="I50" t="n">
-        <v>44.4</v>
+        <v>24.2</v>
       </c>
       <c r="J50" t="n">
-        <v>37</v>
+        <v>39.4</v>
       </c>
       <c r="K50" t="n">
-        <v>0.95</v>
+        <v>1.3</v>
       </c>
       <c r="L50" t="n">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Horsham</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Ebbsfleet United</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1.69</v>
+        <v>2.77</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2772,42 +2772,42 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>56.2</v>
+        <v>46.4</v>
       </c>
       <c r="H51" t="n">
-        <v>18.8</v>
+        <v>35.7</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="J51" t="n">
-        <v>34.4</v>
+        <v>39.3</v>
       </c>
       <c r="K51" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
       <c r="L51" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Al Orubah</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pisa</t>
+          <t>Al Jabalain</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.67</v>
+        <v>2.73</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2818,42 +2818,42 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>56.2</v>
+        <v>46.4</v>
       </c>
       <c r="H52" t="n">
-        <v>18.8</v>
+        <v>35.7</v>
       </c>
       <c r="I52" t="n">
-        <v>25</v>
+        <v>17.9</v>
       </c>
       <c r="J52" t="n">
-        <v>34.4</v>
+        <v>39.3</v>
       </c>
       <c r="K52" t="n">
-        <v>0.93</v>
+        <v>1.28</v>
       </c>
       <c r="L52" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FC Porto B</t>
+          <t>Cheshunt</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pacos Ferreira</t>
+          <t>Aveley</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.02</v>
+        <v>3.22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2864,42 +2864,42 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>45.6</v>
+        <v>38.9</v>
       </c>
       <c r="H53" t="n">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="I53" t="n">
-        <v>36.8</v>
+        <v>44.4</v>
       </c>
       <c r="J53" t="n">
-        <v>35.1</v>
+        <v>61.1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.93</v>
+        <v>1.26</v>
       </c>
       <c r="L53" t="n">
-        <v>57</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Welling United</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Carshalton Athletic</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2910,42 +2910,42 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>44.6</v>
+        <v>48.5</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>27.3</v>
       </c>
       <c r="I54" t="n">
-        <v>30.4</v>
+        <v>24.2</v>
       </c>
       <c r="J54" t="n">
-        <v>48.2</v>
+        <v>48.5</v>
       </c>
       <c r="K54" t="n">
-        <v>0.91</v>
+        <v>1.24</v>
       </c>
       <c r="L54" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Chesham United</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Zaglebie Lubin</t>
+          <t>Dagenham &amp; Redbridge</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2956,42 +2956,42 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="H55" t="n">
-        <v>28.1</v>
+        <v>34.6</v>
       </c>
       <c r="I55" t="n">
-        <v>20.2</v>
+        <v>15.4</v>
       </c>
       <c r="J55" t="n">
-        <v>49.4</v>
+        <v>42.3</v>
       </c>
       <c r="K55" t="n">
-        <v>0.9</v>
+        <v>1.22</v>
       </c>
       <c r="L55" t="n">
-        <v>89</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Brondby</t>
+          <t>Central Cordoba de Santiago</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sonderjyske</t>
+          <t>Talleres Cordoba</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.05</v>
+        <v>3.38</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3002,22 +3002,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>43.4</v>
+        <v>35.7</v>
       </c>
       <c r="H56" t="n">
-        <v>24.1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>32.5</v>
+        <v>64.3</v>
       </c>
       <c r="J56" t="n">
-        <v>41</v>
+        <v>57.1</v>
       </c>
       <c r="K56" t="n">
-        <v>0.89</v>
+        <v>1.2</v>
       </c>
       <c r="L56" t="n">
-        <v>83</v>
+        <v>14</v>
       </c>
     </row>
     <row r="57">
@@ -3028,16 +3028,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>AFC Totton</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Slough Town</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3048,42 +3048,42 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>47.1</v>
+        <v>50</v>
       </c>
       <c r="H57" t="n">
-        <v>28.2</v>
+        <v>18.4</v>
       </c>
       <c r="I57" t="n">
-        <v>24.7</v>
+        <v>31.6</v>
       </c>
       <c r="J57" t="n">
-        <v>38.8</v>
+        <v>47.4</v>
       </c>
       <c r="K57" t="n">
-        <v>0.87</v>
+        <v>1.12</v>
       </c>
       <c r="L57" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Club Queretaro</t>
+          <t>Worthing</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FC Juarez</t>
+          <t>Torquay</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3094,42 +3094,42 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>32.6</v>
+        <v>60.6</v>
       </c>
       <c r="H58" t="n">
-        <v>32.6</v>
+        <v>18.2</v>
       </c>
       <c r="I58" t="n">
-        <v>34.9</v>
+        <v>21.2</v>
       </c>
       <c r="J58" t="n">
-        <v>44.2</v>
+        <v>60.6</v>
       </c>
       <c r="K58" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="L58" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Southend</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Boreham Wood</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3140,42 +3140,42 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>43.5</v>
+        <v>56.3</v>
       </c>
       <c r="H59" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="I59" t="n">
-        <v>39.1</v>
+        <v>26.4</v>
       </c>
       <c r="J59" t="n">
-        <v>26.1</v>
+        <v>55.2</v>
       </c>
       <c r="K59" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="L59" t="n">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Los Angeles Galaxy</t>
+          <t>Tonbridge Angels</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York City FC</t>
+          <t>Hampton &amp; Richmond</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3186,42 +3186,42 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>37.5</v>
+        <v>50.6</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>20.7</v>
       </c>
       <c r="I60" t="n">
-        <v>37.5</v>
+        <v>28.7</v>
       </c>
       <c r="J60" t="n">
-        <v>37.5</v>
+        <v>51.7</v>
       </c>
       <c r="K60" t="n">
-        <v>0.84</v>
+        <v>1.09</v>
       </c>
       <c r="L60" t="n">
-        <v>24</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Watford U21</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tanjong Pagar</t>
+          <t>Brentford U21</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.45</v>
+        <v>2.76</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3232,42 +3232,42 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>57.1</v>
+        <v>39.7</v>
       </c>
       <c r="H61" t="n">
-        <v>22.9</v>
+        <v>27</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="J61" t="n">
-        <v>37.1</v>
+        <v>61.9</v>
       </c>
       <c r="K61" t="n">
-        <v>0.83</v>
+        <v>1.09</v>
       </c>
       <c r="L61" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Persija</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.58</v>
+        <v>3.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3278,42 +3278,42 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>52.9</v>
+        <v>34.3</v>
       </c>
       <c r="H62" t="n">
-        <v>29.4</v>
+        <v>22.9</v>
       </c>
       <c r="I62" t="n">
-        <v>17.6</v>
+        <v>42.9</v>
       </c>
       <c r="J62" t="n">
-        <v>58.8</v>
+        <v>57.1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.82</v>
+        <v>1.08</v>
       </c>
       <c r="L62" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Hamrun Spartans</t>
+          <t>Tiverton Town</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Marsaxlokk</t>
+          <t>Dorchester Town</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1.56</v>
+        <v>2.82</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3324,22 +3324,22 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>52.6</v>
+        <v>36.7</v>
       </c>
       <c r="H63" t="n">
-        <v>24.6</v>
+        <v>30</v>
       </c>
       <c r="I63" t="n">
-        <v>22.8</v>
+        <v>33.3</v>
       </c>
       <c r="J63" t="n">
-        <v>57.9</v>
+        <v>63.3</v>
       </c>
       <c r="K63" t="n">
-        <v>0.82</v>
+        <v>1.05</v>
       </c>
       <c r="L63" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -3350,16 +3350,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Al-Fateh</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Al Okhdood</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1.6</v>
+        <v>3.45</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3370,42 +3370,42 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>48.9</v>
+        <v>30.2</v>
       </c>
       <c r="H64" t="n">
-        <v>34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>17</v>
+        <v>60.5</v>
       </c>
       <c r="J64" t="n">
-        <v>55.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="L64" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Union Santa Fe</t>
+          <t>Cliftonville FC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1.6</v>
+        <v>3.42</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3416,42 +3416,42 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>47.2</v>
+        <v>30.2</v>
       </c>
       <c r="H65" t="n">
-        <v>36.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>16.7</v>
+        <v>60.5</v>
       </c>
       <c r="J65" t="n">
-        <v>69.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>0.78</v>
+        <v>1.04</v>
       </c>
       <c r="L65" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Dunfermline</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Partick</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1.64</v>
+        <v>3.02</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3462,42 +3462,42 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>47.2</v>
+        <v>33.3</v>
       </c>
       <c r="H66" t="n">
-        <v>36.1</v>
+        <v>22.2</v>
       </c>
       <c r="I66" t="n">
-        <v>16.7</v>
+        <v>44.4</v>
       </c>
       <c r="J66" t="n">
-        <v>69.40000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="K66" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="L66" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AFC Bournemouth U21</t>
+          <t>Wealdstone</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Millwall U21</t>
+          <t>Brackley Town</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.39</v>
+        <v>2.05</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3508,42 +3508,42 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>54.8</v>
+        <v>49.3</v>
       </c>
       <c r="H67" t="n">
-        <v>32.3</v>
+        <v>15.5</v>
       </c>
       <c r="I67" t="n">
-        <v>12.9</v>
+        <v>35.2</v>
       </c>
       <c r="J67" t="n">
-        <v>45.2</v>
+        <v>50.7</v>
       </c>
       <c r="K67" t="n">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="L67" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>01:06</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pachuca W</t>
+          <t>Sportfreunde Siegen</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Juárez W</t>
+          <t>Paderborn II</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.35</v>
+        <v>1.73</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3554,42 +3554,42 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>54.8</v>
+        <v>57.7</v>
       </c>
       <c r="H68" t="n">
-        <v>32.3</v>
+        <v>25</v>
       </c>
       <c r="I68" t="n">
-        <v>12.9</v>
+        <v>17.3</v>
       </c>
       <c r="J68" t="n">
-        <v>45.2</v>
+        <v>46.2</v>
       </c>
       <c r="K68" t="n">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="L68" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Al-Hidd</t>
+          <t>Al Tadhamon</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sitra</t>
+          <t>Al Jahra</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3600,42 +3600,42 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>32.3</v>
+        <v>47.1</v>
       </c>
       <c r="H69" t="n">
-        <v>32.3</v>
+        <v>29.4</v>
       </c>
       <c r="I69" t="n">
-        <v>35.5</v>
+        <v>23.5</v>
       </c>
       <c r="J69" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="K69" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="L69" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>West Ham United U21</t>
+          <t>Zaglebie Sosnowiec</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Crystal Palace U21</t>
+          <t>Sandecja Nowy Sącz</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3646,42 +3646,42 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>32.3</v>
+        <v>49.3</v>
       </c>
       <c r="H70" t="n">
-        <v>32.3</v>
+        <v>15.5</v>
       </c>
       <c r="I70" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="J70" t="n">
-        <v>45.2</v>
+        <v>50.7</v>
       </c>
       <c r="K70" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="L70" t="n">
-        <v>31</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Rio Ave U23</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Vizela U23</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.6</v>
+        <v>2.06</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3692,42 +3692,42 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>44.4</v>
+        <v>49.3</v>
       </c>
       <c r="H71" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="I71" t="n">
-        <v>35.6</v>
+        <v>35.2</v>
       </c>
       <c r="J71" t="n">
-        <v>40</v>
+        <v>50.7</v>
       </c>
       <c r="K71" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="L71" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>02:15</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Bradford</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Rotherham</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3738,42 +3738,42 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>52.1</v>
+        <v>60.9</v>
       </c>
       <c r="H72" t="n">
-        <v>22.9</v>
+        <v>30.4</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>64.59999999999999</v>
+        <v>39.1</v>
       </c>
       <c r="K72" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CFRJ / Maricá</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Portuguesa RJ</t>
+          <t>Shrewsbury</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.46</v>
+        <v>1.63</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3784,19 +3784,19 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>28.3</v>
+        <v>60.9</v>
       </c>
       <c r="H73" t="n">
-        <v>34.8</v>
+        <v>30.4</v>
       </c>
       <c r="I73" t="n">
-        <v>37</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J73" t="n">
         <v>39.1</v>
       </c>
       <c r="K73" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>46</v>
@@ -3805,21 +3805,21 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Xelajú</t>
+          <t>Radcliffe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mixco</t>
+          <t>Southport</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3830,42 +3830,42 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>40.4</v>
+        <v>57.3</v>
       </c>
       <c r="H74" t="n">
-        <v>27.7</v>
+        <v>22</v>
       </c>
       <c r="I74" t="n">
-        <v>31.9</v>
+        <v>20.7</v>
       </c>
       <c r="J74" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="K74" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Chelmsford City</t>
+          <t>Al Baten</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hemel Hempstead Town</t>
+          <t>Al Wehda Club</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.08</v>
+        <v>2.85</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3876,42 +3876,42 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>27.6</v>
+        <v>35</v>
       </c>
       <c r="H75" t="n">
-        <v>27.6</v>
+        <v>32.5</v>
       </c>
       <c r="I75" t="n">
-        <v>44.8</v>
+        <v>32.5</v>
       </c>
       <c r="J75" t="n">
-        <v>58.6</v>
+        <v>42.5</v>
       </c>
       <c r="K75" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Leicester City U21</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Manchester United U21</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>3.1</v>
+        <v>1.65</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3922,42 +3922,42 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>17.6</v>
+        <v>60.9</v>
       </c>
       <c r="H76" t="n">
-        <v>23.5</v>
+        <v>30.4</v>
       </c>
       <c r="I76" t="n">
-        <v>58.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>41.2</v>
+        <v>39.1</v>
       </c>
       <c r="K76" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Hereford</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Chester</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3.14</v>
+        <v>2.68</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3968,42 +3968,42 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>14.3</v>
+        <v>37.5</v>
       </c>
       <c r="H77" t="n">
-        <v>21.4</v>
+        <v>33.3</v>
       </c>
       <c r="I77" t="n">
-        <v>64.3</v>
+        <v>29.2</v>
       </c>
       <c r="J77" t="n">
-        <v>50</v>
+        <v>54.2</v>
       </c>
       <c r="K77" t="n">
-        <v>0.45</v>
+        <v>0.99</v>
       </c>
       <c r="L77" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Famalicao</t>
+          <t>Internazionale U19</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Betis U19</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.58</v>
+        <v>2.63</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4014,42 +4014,42 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>18.2</v>
+        <v>37.5</v>
       </c>
       <c r="H78" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="I78" t="n">
-        <v>63.6</v>
+        <v>29.2</v>
       </c>
       <c r="J78" t="n">
-        <v>36.4</v>
+        <v>54.2</v>
       </c>
       <c r="K78" t="n">
-        <v>0.28</v>
+        <v>0.99</v>
       </c>
       <c r="L78" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Platense</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Defensa Y Justicia</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4060,42 +4060,42 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>18.2</v>
+        <v>47.9</v>
       </c>
       <c r="H79" t="n">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="I79" t="n">
-        <v>63.6</v>
+        <v>33.3</v>
       </c>
       <c r="J79" t="n">
-        <v>36.4</v>
+        <v>54.2</v>
       </c>
       <c r="K79" t="n">
-        <v>0.28</v>
+        <v>0.98</v>
       </c>
       <c r="L79" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Wingate &amp; Finchley</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AFC Hermannstadt</t>
+          <t>Canvey Island</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.86</v>
+        <v>1.65</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4106,42 +4106,42 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>7.1</v>
+        <v>58.8</v>
       </c>
       <c r="H80" t="n">
-        <v>28.6</v>
+        <v>17.6</v>
       </c>
       <c r="I80" t="n">
-        <v>64.3</v>
+        <v>23.5</v>
       </c>
       <c r="J80" t="n">
-        <v>71.40000000000001</v>
+        <v>35.3</v>
       </c>
       <c r="K80" t="n">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="L80" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ironi Modi'in</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Glenavon FC</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>3.26</v>
+        <v>1.67</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4152,42 +4152,42 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Al Salmiyah</t>
+          <t>Elgin City</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Edinburgh City</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>4.75</v>
+        <v>1.64</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4198,42 +4198,42 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FK Trakai</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>16.75</v>
+        <v>1.61</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4244,21 +4244,2183 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>58.8</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>35.3</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>0.97</v>
       </c>
       <c r="L83" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Leicester</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I84" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J84" t="n">
+        <v>50</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L84" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Forest Green</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston United</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H85" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I85" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="J85" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="L85" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Banbury United</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Stratford Town</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="H86" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="J86" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="L86" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Macclesfield</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AFC Fylde</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H87" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="I87" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="J87" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="L87" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>KAA Gent II</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Olympic Charleroi</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H88" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I88" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J88" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L88" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>QPR</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H89" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I89" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J89" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L89" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>South Shields</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Worksop Town</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H90" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="I90" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L90" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Gil Vicente U23</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Portimonense U23</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="H91" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="I91" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="J91" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L91" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ind. Yumbo</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Real Santander</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H92" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J92" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L92" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Quindio</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="H93" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="I93" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J93" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L93" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>West Brom</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Charlton</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="H94" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="I94" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J94" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L94" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I95" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="J95" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L95" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Ammanford AFC</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Aberystwyth Town</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="H96" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I96" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>41</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="L96" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Bhayangkara FC</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Semen Padang</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="H97" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="I97" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="J97" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L97" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Bedford Town</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Peterborough Sports</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>40</v>
+      </c>
+      <c r="H98" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I98" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J98" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L98" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dundee Utd</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>40</v>
+      </c>
+      <c r="H99" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="J99" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L99" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Rancho Santana</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Real Madriz</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="I100" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L100" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Maidstone Utd</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Enfield Town</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="H101" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I101" t="n">
+        <v>20</v>
+      </c>
+      <c r="J101" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L101" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Al-Raed</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Al Jubail</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="H102" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="L102" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" t="n">
+        <v>50</v>
+      </c>
+      <c r="H103" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L103" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wigan Athletic U21</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fleetwood Town U21</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>50</v>
+      </c>
+      <c r="H104" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I104" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="J104" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L104" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Lucko</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Trnje</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H105" t="n">
+        <v>34</v>
+      </c>
+      <c r="I105" t="n">
+        <v>17</v>
+      </c>
+      <c r="J105" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="L105" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Buxton</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>King's Lynn Town</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J106" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L106" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Al Bukayriyah</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Al Jandal</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I107" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J107" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="L107" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Hull City</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Derby</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="H108" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="J108" t="n">
+        <v>49</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L108" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Instituto Cordoba</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="I109" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>42</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L109" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Abha</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Al Anwar</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="H110" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="I110" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="J110" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L110" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gainsborough Trinity</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Leek Town</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H111" t="n">
+        <v>20</v>
+      </c>
+      <c r="I111" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="J111" t="n">
+        <v>40</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L111" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Larne</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Linfield</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" t="n">
+        <v>40</v>
+      </c>
+      <c r="J112" t="n">
+        <v>66</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L112" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Estrela U23</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Estoril U23</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="H113" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J113" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="L113" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Kettering Town</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>AFC Sudbury</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J114" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="L114" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Doncaster</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Luton</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H115" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I115" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="J115" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L115" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Blackburn</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H116" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I116" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="J116" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L116" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Hungerford Town</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Bracknell Town</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H117" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I117" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="J117" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="L117" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Palmeiras U20</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>São Paulo U20</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H118" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I118" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J118" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L118" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>United of Manchester</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Stockton Town</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I119" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="J119" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L119" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Al Khaleej Saihat</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H120" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I120" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J120" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L120" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="H121" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I121" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="J121" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L121" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ismaily SC</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="I122" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="J122" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L122" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I123" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="J123" t="n">
+        <v>60</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L123" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Dumbarton</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Clyde</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="H124" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I124" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J124" t="n">
+        <v>50</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L124" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Alvechurch</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Real Bedford</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H125" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="J125" t="n">
+        <v>30</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L125" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ghazl El Mehalla</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Pyramids FC</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Cardiff City U21</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Colchester United U21</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Al-Hazm</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Al-Ittihad FC</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Al Taawon</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Al-Hilal Saudi FC</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Thanh Hóa</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Công An Nhân Dân</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
         <v>0</v>
       </c>
     </row>

--- a/sports_data.xlsx
+++ b/sports_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,21 +493,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST Johnstone</t>
+          <t>PSM Makassar</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>1.97</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -527,79 +527,79 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>7.05</v>
+        <v>1.95</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Flora Tallinn</t>
+          <t>Buriram United</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Khon Kaen United</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4.33</v>
+        <v>1.05</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>100</v>
+        <v>54.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.17</v>
+        <v>1.05</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Castanhal</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Enppi</t>
+          <t>Guarani Campinas</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -619,33 +619,33 @@
         <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Coventry City U21</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sheffield United U21</t>
+          <t>Al-Nassr</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.74</v>
+        <v>10.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -677,25 +677,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amazulu</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Barcelona B</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.75</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -705,39 +705,39 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
         <v>100</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Flint Mountain</t>
+          <t>FC Winterthur</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Llandudno</t>
+          <t>FC Thun</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -757,79 +757,79 @@
         <v>100</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Santos U20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bodo/Glimt</t>
+          <t>Grêmio U20</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>85.2</v>
+        <v>84</v>
       </c>
       <c r="G8" t="n">
-        <v>85.2</v>
+        <v>63</v>
       </c>
       <c r="H8" t="n">
-        <v>14.8</v>
+        <v>25.9</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="J8" t="n">
-        <v>48.1</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
-        <v>1.06</v>
+        <v>0.85</v>
       </c>
       <c r="L8" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FC Eindhoven</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -837,183 +837,183 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>85.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>85.09999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>10.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
-        <v>4.3</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
-        <v>51.1</v>
+        <v>39.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.15</v>
+        <v>1.03</v>
       </c>
       <c r="L9" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Barquereño</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spanish Town Police</t>
+          <t>Tropezón</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1.23</v>
+        <v>6.95</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>82.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
-        <v>82.09999999999999</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>10.7</v>
+        <v>80</v>
       </c>
       <c r="J10" t="n">
-        <v>39.3</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="L10" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>South Melbourne</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tahiti United</t>
+          <t>Gimnasia Chivilcoy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>82.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>82.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>7.1</v>
+        <v>21.1</v>
       </c>
       <c r="I11" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J11" t="n">
-        <v>39.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="L11" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Birkirkara</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Pietà Hotspurs</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.1</v>
+        <v>1.19</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>80</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>80</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>21.1</v>
       </c>
       <c r="I12" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="J12" t="n">
-        <v>40</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>3.32</v>
+        <v>0.79</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Inter San Carlos</t>
+          <t>Ciudad de Lucena</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AD Cofutpa</t>
+          <t>Chiclana</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1045,63 +1045,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Žilina U19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Etar Veliko Tarnovo</t>
+          <t>Club Brugge U19</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.51</v>
+        <v>4.15</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="G14" t="n">
-        <v>77.90000000000001</v>
+        <v>44.4</v>
       </c>
       <c r="H14" t="n">
-        <v>12.8</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>9.300000000000001</v>
+        <v>55.6</v>
       </c>
       <c r="J14" t="n">
-        <v>64</v>
+        <v>77.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.21</v>
+        <v>1.84</v>
       </c>
       <c r="L14" t="n">
-        <v>86</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vardar Skopje</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ohrid</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1137,21 +1137,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sporting Cristal</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Club Brugge KV</t>
+          <t>2 de Mayo</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1159,91 +1159,91 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>75.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>62.2</v>
+        <v>60</v>
       </c>
       <c r="H16" t="n">
-        <v>24.4</v>
+        <v>21.8</v>
       </c>
       <c r="I16" t="n">
-        <v>13.3</v>
+        <v>18.2</v>
       </c>
       <c r="J16" t="n">
-        <v>75.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.84</v>
+        <v>0.87</v>
       </c>
       <c r="L16" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Al Taee</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Inter Kashi</t>
+          <t>Al Arabi SC</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H17" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I17" t="n">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Farense U23</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>União Leiria U23</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1251,45 +1251,45 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>72.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="G18" t="n">
-        <v>72.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="H18" t="n">
-        <v>17.6</v>
+        <v>16</v>
       </c>
       <c r="I18" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="J18" t="n">
-        <v>50.6</v>
+        <v>68</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L18" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Villarreal U19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Qarabag</t>
+          <t>Legia Warszawa U19</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1297,45 +1297,45 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>72.2</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>72.2</v>
+        <v>76</v>
       </c>
       <c r="H19" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="I19" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>72.2</v>
+        <v>68</v>
       </c>
       <c r="K19" t="n">
-        <v>0.83</v>
+        <v>1.1</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maidenhead</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salisbury</t>
+          <t>Nacional AM</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1343,45 +1343,45 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>71.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G20" t="n">
-        <v>71.2</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>17.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>11.5</v>
+        <v>16.3</v>
       </c>
       <c r="J20" t="n">
-        <v>59.6</v>
+        <v>60.5</v>
       </c>
       <c r="K20" t="n">
-        <v>1.03</v>
+        <v>0.93</v>
       </c>
       <c r="L20" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Swansea</t>
+          <t>Ypiranga-RS</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Preston</t>
+          <t>Ji-Paraná</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.74</v>
+        <v>1.22</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1389,117 +1389,117 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>70</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>70</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>16.3</v>
       </c>
       <c r="J21" t="n">
-        <v>46.7</v>
+        <v>60.5</v>
       </c>
       <c r="K21" t="n">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="L21" t="n">
-        <v>60</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Stirling Albion</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Annan Athletic</t>
+          <t>Atlético Alagoinhas</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>3.1</v>
+        <v>1.22</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>60</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>22.9</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="J22" t="n">
-        <v>25.7</v>
+        <v>60.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="L22" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Spennymoor Town</t>
+          <t>Independiente Medellin</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chorley</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>57.1</v>
+        <v>73.2</v>
       </c>
       <c r="G23" t="n">
-        <v>38.1</v>
+        <v>73.2</v>
       </c>
       <c r="H23" t="n">
-        <v>57.1</v>
+        <v>22</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>42.9</v>
+        <v>73.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="L23" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
@@ -1510,154 +1510,154 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Leamington</t>
+          <t>Norwich</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Merthyr Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3.98</v>
+        <v>1.18</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>57.1</v>
+        <v>72.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>72.2</v>
       </c>
       <c r="H24" t="n">
-        <v>57.1</v>
+        <v>16.7</v>
       </c>
       <c r="I24" t="n">
-        <v>42.9</v>
+        <v>11.1</v>
       </c>
       <c r="J24" t="n">
-        <v>28.6</v>
+        <v>72.2</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="L24" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Curzon Ashton</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Darlington 1883</t>
+          <t>Real Jaén</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>56.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>16.2</v>
+        <v>28.6</v>
       </c>
       <c r="H25" t="n">
-        <v>56.8</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>35.1</v>
+        <v>28.6</v>
       </c>
       <c r="K25" t="n">
-        <v>0.48</v>
+        <v>0.76</v>
       </c>
       <c r="L25" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>First Vienna W</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ipswich</t>
+          <t>Neulengbach W</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3.24</v>
+        <v>1.47</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="L26" t="n">
         <v>52</v>
-      </c>
-      <c r="G26" t="n">
-        <v>16</v>
-      </c>
-      <c r="H26" t="n">
-        <v>52</v>
-      </c>
-      <c r="I26" t="n">
-        <v>32</v>
-      </c>
-      <c r="J26" t="n">
-        <v>40</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="L26" t="n">
-        <v>25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FC Halifax Town</t>
+          <t>Al-Faisaly FC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rochdale</t>
+          <t>Al Ula</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1665,45 +1665,45 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>50</v>
+        <v>22.9</v>
       </c>
       <c r="H27" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>17.1</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>25.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.12</v>
+        <v>0.72</v>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Accrington ST</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3.56</v>
+        <v>4.45</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1723,33 +1723,33 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K28" t="n">
-        <v>1.78</v>
+        <v>2.22</v>
       </c>
       <c r="L28" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dover</t>
+          <t>Al-Wasl FC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AFC Hornchurch</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.4</v>
+        <v>3.26</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1757,45 +1757,45 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="G29" t="n">
-        <v>33.3</v>
+        <v>23.1</v>
       </c>
       <c r="H29" t="n">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="I29" t="n">
-        <v>16.7</v>
+        <v>30.8</v>
       </c>
       <c r="J29" t="n">
-        <v>16.7</v>
+        <v>38.5</v>
       </c>
       <c r="K29" t="n">
-        <v>1.15</v>
+        <v>0.75</v>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Union Magdalena</t>
+          <t>Farnborough</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tigres FC</t>
+          <t>Chippenham Town</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1803,45 +1803,45 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>45.7</v>
       </c>
       <c r="G30" t="n">
-        <v>50</v>
+        <v>39.1</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>45.7</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>15.2</v>
       </c>
       <c r="J30" t="n">
-        <v>25</v>
+        <v>31.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="L30" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bath City</t>
+          <t>RB Bragantino</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Weston-super-Mare</t>
+          <t>Atletico Paranaense</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.71</v>
+        <v>1.72</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1849,45 +1849,45 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>50</v>
+        <v>44.8</v>
       </c>
       <c r="G31" t="n">
-        <v>25</v>
+        <v>40.3</v>
       </c>
       <c r="H31" t="n">
-        <v>50</v>
+        <v>44.8</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>14.9</v>
       </c>
       <c r="J31" t="n">
-        <v>50</v>
+        <v>31.3</v>
       </c>
       <c r="K31" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="L31" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nam Dinh</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.39</v>
+        <v>2.94</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1895,45 +1895,45 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>48.9</v>
+        <v>42.9</v>
       </c>
       <c r="G32" t="n">
-        <v>27.7</v>
+        <v>38.1</v>
       </c>
       <c r="H32" t="n">
-        <v>48.9</v>
+        <v>42.9</v>
       </c>
       <c r="I32" t="n">
-        <v>23.4</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>42.6</v>
+        <v>38.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.65</v>
+        <v>1.12</v>
       </c>
       <c r="L32" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Hanwell Town</t>
+          <t>Ceilândia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plymouth Parkway</t>
+          <t>Jacuipense</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.74</v>
+        <v>2.43</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1941,45 +1941,45 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>44.8</v>
+        <v>41</v>
       </c>
       <c r="G33" t="n">
-        <v>40.3</v>
+        <v>26.5</v>
       </c>
       <c r="H33" t="n">
-        <v>44.8</v>
+        <v>41</v>
       </c>
       <c r="I33" t="n">
-        <v>14.9</v>
+        <v>32.5</v>
       </c>
       <c r="J33" t="n">
-        <v>31.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.71</v>
+        <v>0.65</v>
       </c>
       <c r="L33" t="n">
-        <v>67</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bayern München II</t>
+          <t>San Martin S.J.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SpVgg Unterhaching</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.99</v>
+        <v>2.21</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>42.9</v>
+        <v>40.6</v>
       </c>
       <c r="G34" t="n">
-        <v>38.1</v>
+        <v>15.6</v>
       </c>
       <c r="H34" t="n">
-        <v>42.9</v>
+        <v>40.6</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>43.8</v>
       </c>
       <c r="J34" t="n">
-        <v>38.1</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>1.12</v>
+        <v>0.35</v>
       </c>
       <c r="L34" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -2016,16 +2016,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Eastbourne Borough</t>
+          <t>Braintree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dorking Wanderers</t>
+          <t>Aldershot Town</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2036,42 +2036,42 @@
         <v>40</v>
       </c>
       <c r="G35" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
         <v>40</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J35" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>2.31</v>
+        <v>0.75</v>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Concordia</t>
+          <t>Noja</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Vimenor</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.62</v>
+        <v>3.92</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2082,38 +2082,38 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>60</v>
+        <v>66.7</v>
       </c>
       <c r="H36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="K36" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="L36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Eintracht Frankf U19</t>
+          <t>Gimnasia M.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sporting CP U19</t>
+          <t>Independiente</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2149,21 +2149,21 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2174,42 +2174,42 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>68</v>
+        <v>53.8</v>
       </c>
       <c r="H38" t="n">
-        <v>8</v>
+        <v>30.8</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>15.4</v>
       </c>
       <c r="J38" t="n">
-        <v>68</v>
+        <v>46.2</v>
       </c>
       <c r="K38" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="L38" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Masr</t>
+          <t>Airdrie United</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Zamalek SC</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.42</v>
+        <v>2.76</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2220,42 +2220,42 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>53.8</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>30.8</v>
+        <v>17.9</v>
       </c>
       <c r="I39" t="n">
-        <v>15.4</v>
+        <v>17.9</v>
       </c>
       <c r="J39" t="n">
-        <v>46.2</v>
+        <v>69.2</v>
       </c>
       <c r="K39" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="L39" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Scunthorpe</t>
+          <t>remo</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>York</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2269,16 +2269,16 @@
         <v>53.8</v>
       </c>
       <c r="H40" t="n">
-        <v>23.1</v>
+        <v>30.8</v>
       </c>
       <c r="I40" t="n">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="J40" t="n">
-        <v>61.5</v>
+        <v>53.8</v>
       </c>
       <c r="K40" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="L40" t="n">
         <v>13</v>
@@ -2287,21 +2287,21 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oxford City</t>
+          <t>Lamphun Warrior</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AFC Telford United</t>
+          <t>Bangkok United</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2312,42 +2312,42 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>53.8</v>
+        <v>47.6</v>
       </c>
       <c r="H41" t="n">
-        <v>23.1</v>
+        <v>9.5</v>
       </c>
       <c r="I41" t="n">
-        <v>23.1</v>
+        <v>42.9</v>
       </c>
       <c r="J41" t="n">
-        <v>61.5</v>
+        <v>42.9</v>
       </c>
       <c r="K41" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="L41" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dulwich Hamlet</t>
+          <t>Nakhon Ratchasima FC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chatham Town</t>
+          <t>Rayong FC</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.22</v>
+        <v>3.28</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2379,21 +2379,21 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Northampton</t>
+          <t>Gimnasia L.P.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.33</v>
+        <v>3.04</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2404,22 +2404,22 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>65.7</v>
+        <v>50</v>
       </c>
       <c r="H43" t="n">
-        <v>11.4</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>22.9</v>
+        <v>50</v>
       </c>
       <c r="J43" t="n">
-        <v>37.1</v>
+        <v>50</v>
       </c>
       <c r="K43" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="L43" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44">
@@ -2430,16 +2430,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alfreton Town</t>
+          <t>Hartlepool</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Scarborough Athletic</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.54</v>
+        <v>3.02</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2450,42 +2450,42 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>56.7</v>
+        <v>50</v>
       </c>
       <c r="H44" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="J44" t="n">
         <v>50</v>
       </c>
       <c r="K44" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="L44" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Ayr Utd</t>
+          <t>Laktaši</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2496,42 +2496,42 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>56.7</v>
+        <v>57.6</v>
       </c>
       <c r="H45" t="n">
-        <v>26.7</v>
+        <v>18.2</v>
       </c>
       <c r="I45" t="n">
-        <v>16.7</v>
+        <v>24.2</v>
       </c>
       <c r="J45" t="n">
-        <v>50</v>
+        <v>39.4</v>
       </c>
       <c r="K45" t="n">
-        <v>1.45</v>
+        <v>1.3</v>
       </c>
       <c r="L45" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Trefelin</t>
+          <t>Achuapa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cambrian &amp; Clydach</t>
+          <t>Xelajú</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.74</v>
+        <v>2.41</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2542,42 +2542,42 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="H46" t="n">
-        <v>38.1</v>
+        <v>34.6</v>
       </c>
       <c r="I46" t="n">
-        <v>9.5</v>
+        <v>15.4</v>
       </c>
       <c r="J46" t="n">
-        <v>38.1</v>
+        <v>42.3</v>
       </c>
       <c r="K46" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="L46" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Sportivo Ameliano</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2588,42 +2588,42 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>66.2</v>
+        <v>33.3</v>
       </c>
       <c r="H47" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="I47" t="n">
-        <v>11.8</v>
+        <v>44.4</v>
       </c>
       <c r="J47" t="n">
-        <v>69.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="K47" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="L47" t="n">
-        <v>68</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Charlton Athletic U21</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Swansea City U21</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.13</v>
+        <v>3.34</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2634,42 +2634,42 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>66.2</v>
+        <v>35.7</v>
       </c>
       <c r="H48" t="n">
-        <v>22.1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>11.8</v>
+        <v>64.3</v>
       </c>
       <c r="J48" t="n">
-        <v>69.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="K48" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="L48" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bristol City U21</t>
+          <t>Yeovil Town</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Queens Park Rangers U21</t>
+          <t>Sutton Utd</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2680,42 +2680,42 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>59.7</v>
+        <v>48.5</v>
       </c>
       <c r="H49" t="n">
-        <v>29.2</v>
+        <v>30.3</v>
       </c>
       <c r="I49" t="n">
-        <v>11.1</v>
+        <v>21.2</v>
       </c>
       <c r="J49" t="n">
-        <v>50</v>
+        <v>48.5</v>
       </c>
       <c r="K49" t="n">
-        <v>1.34</v>
+        <v>1.14</v>
       </c>
       <c r="L49" t="n">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tamworth</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Altrincham</t>
+          <t>Teruel</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2726,42 +2726,42 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>57.6</v>
+        <v>50</v>
       </c>
       <c r="H50" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="I50" t="n">
-        <v>24.2</v>
+        <v>31.6</v>
       </c>
       <c r="J50" t="n">
-        <v>39.4</v>
+        <v>47.4</v>
       </c>
       <c r="K50" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="L50" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Horsham</t>
+          <t>Sao Bento</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ebbsfleet United</t>
+          <t>Linense</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.77</v>
+        <v>3.08</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2772,42 +2772,42 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>46.4</v>
+        <v>33.3</v>
       </c>
       <c r="H51" t="n">
-        <v>35.7</v>
+        <v>5.6</v>
       </c>
       <c r="I51" t="n">
-        <v>17.9</v>
+        <v>61.1</v>
       </c>
       <c r="J51" t="n">
-        <v>39.3</v>
+        <v>61.1</v>
       </c>
       <c r="K51" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="L51" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Al Orubah</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Al Jabalain</t>
+          <t>Thor Akureyri</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.73</v>
+        <v>3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2818,42 +2818,42 @@
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>46.4</v>
+        <v>33.3</v>
       </c>
       <c r="H52" t="n">
-        <v>35.7</v>
+        <v>22.2</v>
       </c>
       <c r="I52" t="n">
-        <v>17.9</v>
+        <v>44.4</v>
       </c>
       <c r="J52" t="n">
-        <v>39.3</v>
+        <v>55.6</v>
       </c>
       <c r="K52" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="L52" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cheshunt</t>
+          <t>Oita Trinita</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Aveley</t>
+          <t>Biwako Shiga</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.22</v>
+        <v>1.53</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2864,42 +2864,42 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>38.9</v>
+        <v>65.8</v>
       </c>
       <c r="H53" t="n">
-        <v>16.7</v>
+        <v>18.4</v>
       </c>
       <c r="I53" t="n">
-        <v>44.4</v>
+        <v>15.8</v>
       </c>
       <c r="J53" t="n">
-        <v>61.1</v>
+        <v>39.5</v>
       </c>
       <c r="K53" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="L53" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Welling United</t>
+          <t>Ayutthaya FC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Carshalton Athletic</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2910,42 +2910,42 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>48.5</v>
+        <v>33.3</v>
       </c>
       <c r="H54" t="n">
-        <v>27.3</v>
+        <v>5.6</v>
       </c>
       <c r="I54" t="n">
-        <v>24.2</v>
+        <v>61.1</v>
       </c>
       <c r="J54" t="n">
-        <v>48.5</v>
+        <v>61.1</v>
       </c>
       <c r="K54" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="L54" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chesham United</t>
+          <t>Inter De Limeira</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dagenham &amp; Redbridge</t>
+          <t>Oeste</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2956,42 +2956,42 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>50</v>
+        <v>49.3</v>
       </c>
       <c r="H55" t="n">
-        <v>34.6</v>
+        <v>15.5</v>
       </c>
       <c r="I55" t="n">
-        <v>15.4</v>
+        <v>35.2</v>
       </c>
       <c r="J55" t="n">
-        <v>42.3</v>
+        <v>50.7</v>
       </c>
       <c r="K55" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="L55" t="n">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Central Cordoba de Santiago</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Talleres Cordoba</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3.38</v>
+        <v>2.16</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3002,42 +3002,42 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>35.7</v>
+        <v>47.2</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>28.3</v>
       </c>
       <c r="I56" t="n">
-        <v>64.3</v>
+        <v>24.5</v>
       </c>
       <c r="J56" t="n">
-        <v>57.1</v>
+        <v>52.8</v>
       </c>
       <c r="K56" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="L56" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AFC Totton</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slough Town</t>
+          <t>Cordoba</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3048,42 +3048,42 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H57" t="n">
-        <v>18.4</v>
+        <v>32.5</v>
       </c>
       <c r="I57" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="J57" t="n">
-        <v>47.4</v>
+        <v>42.5</v>
       </c>
       <c r="K57" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Worthing</t>
+          <t>América Mineiro U20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Torquay</t>
+          <t>Fluminense U20</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3094,42 +3094,42 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>60.6</v>
+        <v>37.5</v>
       </c>
       <c r="H58" t="n">
-        <v>18.2</v>
+        <v>33.3</v>
       </c>
       <c r="I58" t="n">
-        <v>21.2</v>
+        <v>29.2</v>
       </c>
       <c r="J58" t="n">
-        <v>60.6</v>
+        <v>54.2</v>
       </c>
       <c r="K58" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="L58" t="n">
-        <v>66</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Southend</t>
+          <t>Belgrano Cordoba</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boreham Wood</t>
+          <t>Atletico Tucuman</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.99</v>
+        <v>1.69</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3140,42 +3140,42 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>56.3</v>
+        <v>58.8</v>
       </c>
       <c r="H59" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="I59" t="n">
-        <v>26.4</v>
+        <v>23.5</v>
       </c>
       <c r="J59" t="n">
-        <v>55.2</v>
+        <v>35.3</v>
       </c>
       <c r="K59" t="n">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="L59" t="n">
-        <v>87</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tonbridge Angels</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hampton &amp; Richmond</t>
+          <t>Chapecoense-sc</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3186,42 +3186,42 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>50.6</v>
+        <v>61.5</v>
       </c>
       <c r="H60" t="n">
-        <v>20.7</v>
+        <v>15.4</v>
       </c>
       <c r="I60" t="n">
-        <v>28.7</v>
+        <v>23.1</v>
       </c>
       <c r="J60" t="n">
-        <v>51.7</v>
+        <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>1.09</v>
+        <v>0.95</v>
       </c>
       <c r="L60" t="n">
-        <v>87</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Watford U21</t>
+          <t>Al Wahda FC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brentford U21</t>
+          <t>Ajman</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.76</v>
+        <v>1.57</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3232,42 +3232,42 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>39.7</v>
+        <v>60.5</v>
       </c>
       <c r="H61" t="n">
-        <v>27</v>
+        <v>21.1</v>
       </c>
       <c r="I61" t="n">
-        <v>33.3</v>
+        <v>18.4</v>
       </c>
       <c r="J61" t="n">
-        <v>61.9</v>
+        <v>60.5</v>
       </c>
       <c r="K61" t="n">
-        <v>1.09</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Persija</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>34.3</v>
+        <v>45.6</v>
       </c>
       <c r="H62" t="n">
-        <v>22.9</v>
+        <v>17.5</v>
       </c>
       <c r="I62" t="n">
-        <v>42.9</v>
+        <v>36.8</v>
       </c>
       <c r="J62" t="n">
-        <v>57.1</v>
+        <v>35.1</v>
       </c>
       <c r="K62" t="n">
-        <v>1.08</v>
+        <v>0.93</v>
       </c>
       <c r="L62" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63">
@@ -3304,16 +3304,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tiverton Town</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dorchester Town</t>
+          <t>Birmingham</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3324,42 +3324,42 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>36.7</v>
+        <v>37.5</v>
       </c>
       <c r="H63" t="n">
-        <v>30</v>
+        <v>17.9</v>
       </c>
       <c r="I63" t="n">
-        <v>33.3</v>
+        <v>44.6</v>
       </c>
       <c r="J63" t="n">
-        <v>63.3</v>
+        <v>37.5</v>
       </c>
       <c r="K63" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
       <c r="L63" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sheffield Utd</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.45</v>
+        <v>2.42</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3370,42 +3370,42 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>30.2</v>
+        <v>37.5</v>
       </c>
       <c r="H64" t="n">
-        <v>9.300000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="I64" t="n">
-        <v>60.5</v>
+        <v>44.6</v>
       </c>
       <c r="J64" t="n">
-        <v>65.09999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="K64" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="L64" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cliftonville FC</t>
+          <t>Gzira United</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Hibernians</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3416,42 +3416,42 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>30.2</v>
+        <v>37.5</v>
       </c>
       <c r="H65" t="n">
-        <v>9.300000000000001</v>
+        <v>17.9</v>
       </c>
       <c r="I65" t="n">
-        <v>60.5</v>
+        <v>44.6</v>
       </c>
       <c r="J65" t="n">
-        <v>65.09999999999999</v>
+        <v>37.5</v>
       </c>
       <c r="K65" t="n">
-        <v>1.04</v>
+        <v>0.92</v>
       </c>
       <c r="L65" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dunfermline</t>
+          <t>Selaya</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Partick</t>
+          <t>Guarnizo</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3462,42 +3462,42 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>33.3</v>
+        <v>27.3</v>
       </c>
       <c r="H66" t="n">
-        <v>22.2</v>
+        <v>36.4</v>
       </c>
       <c r="I66" t="n">
-        <v>44.4</v>
+        <v>36.4</v>
       </c>
       <c r="J66" t="n">
-        <v>55.6</v>
+        <v>45.5</v>
       </c>
       <c r="K66" t="n">
-        <v>1.02</v>
+        <v>0.91</v>
       </c>
       <c r="L66" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Wealdstone</t>
+          <t>Real Madrid U19</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Brackley Town</t>
+          <t>Chelsea U19</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3508,42 +3508,42 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>49.3</v>
+        <v>46.9</v>
       </c>
       <c r="H67" t="n">
-        <v>15.5</v>
+        <v>24.5</v>
       </c>
       <c r="I67" t="n">
-        <v>35.2</v>
+        <v>28.6</v>
       </c>
       <c r="J67" t="n">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="K67" t="n">
-        <v>1.01</v>
+        <v>0.91</v>
       </c>
       <c r="L67" t="n">
-        <v>71</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sportfreunde Siegen</t>
+          <t>Antigua GFC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Paderborn II</t>
+          <t>Guastatoya</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3554,42 +3554,42 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>57.7</v>
+        <v>57.1</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>22.4</v>
       </c>
       <c r="I68" t="n">
-        <v>17.3</v>
+        <v>20.4</v>
       </c>
       <c r="J68" t="n">
-        <v>46.2</v>
+        <v>38.8</v>
       </c>
       <c r="K68" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="L68" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Al Tadhamon</t>
+          <t>Al Zulfi</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Al Jahra</t>
+          <t>Al-Adalah</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3600,42 +3600,42 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>47.1</v>
+        <v>53.8</v>
       </c>
       <c r="H69" t="n">
-        <v>29.4</v>
+        <v>28.2</v>
       </c>
       <c r="I69" t="n">
-        <v>23.5</v>
+        <v>17.9</v>
       </c>
       <c r="J69" t="n">
-        <v>45.1</v>
+        <v>53.8</v>
       </c>
       <c r="K69" t="n">
-        <v>1.01</v>
+        <v>0.89</v>
       </c>
       <c r="L69" t="n">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Zaglebie Sosnowiec</t>
+          <t>Velez Sarsfield</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sandecja Nowy Sącz</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3646,42 +3646,42 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>49.3</v>
+        <v>47.7</v>
       </c>
       <c r="H70" t="n">
-        <v>15.5</v>
+        <v>27.9</v>
       </c>
       <c r="I70" t="n">
-        <v>35.2</v>
+        <v>24.4</v>
       </c>
       <c r="J70" t="n">
-        <v>50.7</v>
+        <v>38.4</v>
       </c>
       <c r="K70" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="L70" t="n">
-        <v>71</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rio Ave U23</t>
+          <t>AL Masry</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Vizela U23</t>
+          <t>Future FC</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3692,42 +3692,42 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>49.3</v>
+        <v>41.1</v>
       </c>
       <c r="H71" t="n">
-        <v>15.5</v>
+        <v>35.7</v>
       </c>
       <c r="I71" t="n">
-        <v>35.2</v>
+        <v>23.2</v>
       </c>
       <c r="J71" t="n">
-        <v>50.7</v>
+        <v>46.4</v>
       </c>
       <c r="K71" t="n">
-        <v>1.01</v>
+        <v>0.88</v>
       </c>
       <c r="L71" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bradford</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rotherham</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3738,42 +3738,42 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>60.9</v>
+        <v>47.7</v>
       </c>
       <c r="H72" t="n">
-        <v>30.4</v>
+        <v>27.9</v>
       </c>
       <c r="I72" t="n">
-        <v>8.699999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="J72" t="n">
-        <v>39.1</v>
+        <v>38.4</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="L72" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Huddersfield Town U21</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shrewsbury</t>
+          <t>Hull City U21</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3784,42 +3784,42 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>60.9</v>
+        <v>47.7</v>
       </c>
       <c r="H73" t="n">
-        <v>30.4</v>
+        <v>27.9</v>
       </c>
       <c r="I73" t="n">
-        <v>8.699999999999999</v>
+        <v>24.4</v>
       </c>
       <c r="J73" t="n">
-        <v>39.1</v>
+        <v>38.4</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="L73" t="n">
-        <v>46</v>
+        <v>86</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Radcliffe</t>
+          <t>Newells Old Boys</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Southport</t>
+          <t>Estudiantes L.P.</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3830,42 +3830,42 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>57.3</v>
+        <v>26.7</v>
       </c>
       <c r="H74" t="n">
-        <v>22</v>
+        <v>26.7</v>
       </c>
       <c r="I74" t="n">
-        <v>20.7</v>
+        <v>46.7</v>
       </c>
       <c r="J74" t="n">
-        <v>47.6</v>
+        <v>20</v>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>0.87</v>
       </c>
       <c r="L74" t="n">
-        <v>82</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Al Baten</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Al Wehda Club</t>
+          <t>Libertad Asuncion</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.85</v>
+        <v>2.15</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3876,42 +3876,42 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H75" t="n">
-        <v>32.5</v>
+        <v>23.1</v>
       </c>
       <c r="I75" t="n">
-        <v>32.5</v>
+        <v>36.9</v>
       </c>
       <c r="J75" t="n">
-        <v>42.5</v>
+        <v>69.2</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="L75" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Leixões U23</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Academico Viseu U23</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.65</v>
+        <v>2.82</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3922,42 +3922,42 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>60.9</v>
+        <v>30</v>
       </c>
       <c r="H76" t="n">
-        <v>30.4</v>
+        <v>30</v>
       </c>
       <c r="I76" t="n">
-        <v>8.699999999999999</v>
+        <v>40</v>
       </c>
       <c r="J76" t="n">
-        <v>39.1</v>
+        <v>60</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="L76" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Hereford</t>
+          <t>Flamengo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chester</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>2.68</v>
+        <v>1.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3968,42 +3968,42 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>37.5</v>
+        <v>57.1</v>
       </c>
       <c r="H77" t="n">
-        <v>33.3</v>
+        <v>22.9</v>
       </c>
       <c r="I77" t="n">
-        <v>29.2</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>54.2</v>
+        <v>37.1</v>
       </c>
       <c r="K77" t="n">
-        <v>0.99</v>
+        <v>0.83</v>
       </c>
       <c r="L77" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Internazionale U19</t>
+          <t>Al-Fayha</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Real Betis U19</t>
+          <t>NEOM</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4014,42 +4014,42 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="H78" t="n">
         <v>37.5</v>
       </c>
-      <c r="H78" t="n">
-        <v>33.3</v>
-      </c>
       <c r="I78" t="n">
-        <v>29.2</v>
+        <v>31.2</v>
       </c>
       <c r="J78" t="n">
-        <v>54.2</v>
+        <v>43.8</v>
       </c>
       <c r="K78" t="n">
-        <v>0.99</v>
+        <v>0.83</v>
       </c>
       <c r="L78" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Platense</t>
+          <t>Zeljeznicar Sarajevo</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Defensa Y Justicia</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>2.08</v>
+        <v>1.56</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4060,42 +4060,42 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>47.9</v>
+        <v>52.9</v>
       </c>
       <c r="H79" t="n">
-        <v>18.8</v>
+        <v>29.4</v>
       </c>
       <c r="I79" t="n">
-        <v>33.3</v>
+        <v>17.6</v>
       </c>
       <c r="J79" t="n">
-        <v>54.2</v>
+        <v>58.8</v>
       </c>
       <c r="K79" t="n">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="L79" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Wingate &amp; Finchley</t>
+          <t>Monte Azul</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Canvey Island</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4106,42 +4106,42 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>58.8</v>
+        <v>30.8</v>
       </c>
       <c r="H80" t="n">
-        <v>17.6</v>
+        <v>34.6</v>
       </c>
       <c r="I80" t="n">
-        <v>23.5</v>
+        <v>34.6</v>
       </c>
       <c r="J80" t="n">
-        <v>35.3</v>
+        <v>46.2</v>
       </c>
       <c r="K80" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="L80" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>SG Sonnenhof Grossaspach</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Glenavon FC</t>
+          <t>Freiburg II</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4152,19 +4152,19 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H81" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I81" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J81" t="n">
         <v>58.8</v>
       </c>
-      <c r="H81" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I81" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="J81" t="n">
-        <v>35.3</v>
-      </c>
       <c r="K81" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="L81" t="n">
         <v>34</v>
@@ -4173,21 +4173,21 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Elgin City</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Edinburgh City</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4198,42 +4198,42 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>58.8</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H82" t="n">
-        <v>17.6</v>
+        <v>15.6</v>
       </c>
       <c r="I82" t="n">
-        <v>23.5</v>
+        <v>18.8</v>
       </c>
       <c r="J82" t="n">
-        <v>35.3</v>
+        <v>59.4</v>
       </c>
       <c r="K82" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="L82" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Benfica</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4244,19 +4244,19 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="H83" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="I83" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="J83" t="n">
         <v>58.8</v>
       </c>
-      <c r="H83" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I83" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="J83" t="n">
-        <v>35.3</v>
-      </c>
       <c r="K83" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="L83" t="n">
         <v>34</v>
@@ -4265,21 +4265,21 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Benfica U19</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Leicester</t>
+          <t>AZ U19</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4290,22 +4290,22 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>61.5</v>
+        <v>52.6</v>
       </c>
       <c r="H84" t="n">
-        <v>15.4</v>
+        <v>24.6</v>
       </c>
       <c r="I84" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="J84" t="n">
-        <v>50</v>
+        <v>57.9</v>
       </c>
       <c r="K84" t="n">
-        <v>0.95</v>
+        <v>0.82</v>
       </c>
       <c r="L84" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
     </row>
     <row r="85">
@@ -4316,16 +4316,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Forest Green</t>
+          <t>Woking</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston United</t>
+          <t>Solihull Moors</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1.51</v>
+        <v>2.21</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4336,42 +4336,42 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>60.5</v>
+        <v>36</v>
       </c>
       <c r="H85" t="n">
-        <v>21.1</v>
+        <v>28</v>
       </c>
       <c r="I85" t="n">
-        <v>18.4</v>
+        <v>36</v>
       </c>
       <c r="J85" t="n">
-        <v>60.5</v>
+        <v>36</v>
       </c>
       <c r="K85" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Banbury United</t>
+          <t>Águilas</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Stratford Town</t>
+          <t>Recreativo Huelva</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.01</v>
+        <v>2.23</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4382,42 +4382,42 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>45.6</v>
+        <v>36</v>
       </c>
       <c r="H86" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="I86" t="n">
-        <v>36.8</v>
+        <v>36</v>
       </c>
       <c r="J86" t="n">
-        <v>35.1</v>
+        <v>36</v>
       </c>
       <c r="K86" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Macclesfield</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AFC Fylde</t>
+          <t>Sevilla Atletico</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.43</v>
+        <v>1.64</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4428,42 +4428,42 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>37.5</v>
+        <v>47.5</v>
       </c>
       <c r="H87" t="n">
-        <v>17.9</v>
+        <v>35</v>
       </c>
       <c r="I87" t="n">
-        <v>44.6</v>
+        <v>17.5</v>
       </c>
       <c r="J87" t="n">
-        <v>37.5</v>
+        <v>45</v>
       </c>
       <c r="K87" t="n">
-        <v>0.92</v>
+        <v>0.78</v>
       </c>
       <c r="L87" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Santo André</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Sertãozinho</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4474,42 +4474,42 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>51.7</v>
+        <v>39.3</v>
       </c>
       <c r="H88" t="n">
-        <v>28.1</v>
+        <v>14.3</v>
       </c>
       <c r="I88" t="n">
-        <v>20.2</v>
+        <v>46.4</v>
       </c>
       <c r="J88" t="n">
-        <v>49.4</v>
+        <v>50</v>
       </c>
       <c r="K88" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="L88" t="n">
-        <v>89</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QPR</t>
+          <t>Sportivo Luqueno</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4520,42 +4520,42 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>51.7</v>
+        <v>32.7</v>
       </c>
       <c r="H89" t="n">
-        <v>28.1</v>
+        <v>22.4</v>
       </c>
       <c r="I89" t="n">
-        <v>20.2</v>
+        <v>44.9</v>
       </c>
       <c r="J89" t="n">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="K89" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="L89" t="n">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>South Shields</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Worksop Town</t>
+          <t>Prachuap</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.31</v>
+        <v>2.33</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4566,42 +4566,42 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>66.7</v>
+        <v>32.7</v>
       </c>
       <c r="H90" t="n">
-        <v>15.4</v>
+        <v>22.4</v>
       </c>
       <c r="I90" t="n">
-        <v>17.9</v>
+        <v>44.9</v>
       </c>
       <c r="J90" t="n">
-        <v>33.3</v>
+        <v>49</v>
       </c>
       <c r="K90" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="L90" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gil Vicente U23</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portimonense U23</t>
+          <t>Cianorte</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4612,42 +4612,42 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>51.7</v>
+        <v>33.3</v>
       </c>
       <c r="H91" t="n">
-        <v>28.1</v>
+        <v>27.5</v>
       </c>
       <c r="I91" t="n">
-        <v>20.2</v>
+        <v>39.1</v>
       </c>
       <c r="J91" t="n">
-        <v>49.4</v>
+        <v>42</v>
       </c>
       <c r="K91" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="L91" t="n">
-        <v>89</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ind. Yumbo</t>
+          <t>Béchar Djedid</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Real Santander</t>
+          <t>MC Saida</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.6</v>
+        <v>2.89</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4658,42 +4658,42 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
       <c r="H92" t="n">
-        <v>28.2</v>
+        <v>37.5</v>
       </c>
       <c r="I92" t="n">
-        <v>17.9</v>
+        <v>37.5</v>
       </c>
       <c r="J92" t="n">
-        <v>53.8</v>
+        <v>12.5</v>
       </c>
       <c r="K92" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="L92" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>America-RN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Quindio</t>
+          <t>GAS</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.79</v>
+        <v>1.14</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4704,42 +4704,42 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>50.6</v>
+        <v>61.9</v>
       </c>
       <c r="H93" t="n">
-        <v>32.5</v>
+        <v>28.6</v>
       </c>
       <c r="I93" t="n">
-        <v>16.9</v>
+        <v>9.5</v>
       </c>
       <c r="J93" t="n">
-        <v>68.8</v>
+        <v>28.6</v>
       </c>
       <c r="K93" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="L93" t="n">
-        <v>77</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>West Brom</t>
+          <t>Sporting Braga U23</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlton</t>
+          <t>Torreense U23</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1.98</v>
+        <v>2.81</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4750,42 +4750,42 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>45.5</v>
+        <v>25</v>
       </c>
       <c r="H94" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="I94" t="n">
-        <v>19.7</v>
+        <v>37.5</v>
       </c>
       <c r="J94" t="n">
-        <v>42.4</v>
+        <v>12.5</v>
       </c>
       <c r="K94" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="L94" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Kidderminster Harriers</t>
+          <t>PSG U19</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Marine</t>
+          <t>HJK U19</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4796,42 +4796,42 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>57.1</v>
+        <v>61.9</v>
       </c>
       <c r="H95" t="n">
-        <v>22.4</v>
+        <v>28.6</v>
       </c>
       <c r="I95" t="n">
-        <v>20.4</v>
+        <v>9.5</v>
       </c>
       <c r="J95" t="n">
-        <v>38.8</v>
+        <v>28.6</v>
       </c>
       <c r="K95" t="n">
-        <v>0.89</v>
+        <v>0.71</v>
       </c>
       <c r="L95" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ammanford AFC</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Aberystwyth Town</t>
+          <t>Votuporanguense</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>2.01</v>
+        <v>1.69</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4842,42 +4842,42 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>43.4</v>
+        <v>41.1</v>
       </c>
       <c r="H96" t="n">
-        <v>24.1</v>
+        <v>27.4</v>
       </c>
       <c r="I96" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="J96" t="n">
-        <v>41</v>
+        <v>49.5</v>
       </c>
       <c r="K96" t="n">
-        <v>0.89</v>
+        <v>0.68</v>
       </c>
       <c r="L96" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bhayangkara FC</t>
+          <t>Taunton Town</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Wimborne Town</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1.81</v>
+        <v>2.48</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4888,42 +4888,42 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>47.7</v>
+        <v>27.5</v>
       </c>
       <c r="H97" t="n">
-        <v>27.9</v>
+        <v>15.7</v>
       </c>
       <c r="I97" t="n">
-        <v>24.4</v>
+        <v>56.9</v>
       </c>
       <c r="J97" t="n">
-        <v>38.4</v>
+        <v>58.8</v>
       </c>
       <c r="K97" t="n">
-        <v>0.88</v>
+        <v>0.67</v>
       </c>
       <c r="L97" t="n">
-        <v>86</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bedford Town</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Peterborough Sports</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4934,42 +4934,42 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="H98" t="n">
-        <v>23.1</v>
+        <v>17.1</v>
       </c>
       <c r="I98" t="n">
-        <v>36.9</v>
+        <v>54.3</v>
       </c>
       <c r="J98" t="n">
-        <v>69.2</v>
+        <v>45.7</v>
       </c>
       <c r="K98" t="n">
-        <v>0.86</v>
+        <v>0.67</v>
       </c>
       <c r="L98" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dundee Utd</t>
+          <t>São Luiz</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Aberdeen</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -4980,42 +4980,42 @@
         <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>40</v>
+        <v>31.7</v>
       </c>
       <c r="H99" t="n">
-        <v>23.1</v>
+        <v>15.9</v>
       </c>
       <c r="I99" t="n">
-        <v>36.9</v>
+        <v>52.4</v>
       </c>
       <c r="J99" t="n">
-        <v>69.2</v>
+        <v>30.2</v>
       </c>
       <c r="K99" t="n">
-        <v>0.86</v>
+        <v>0.65</v>
       </c>
       <c r="L99" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Rancho Santana</t>
+          <t>Água Santa</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Real Madriz</t>
+          <t>Grêmio Prudente</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5026,22 +5026,22 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>43.5</v>
+        <v>31.7</v>
       </c>
       <c r="H100" t="n">
-        <v>17.4</v>
+        <v>15.9</v>
       </c>
       <c r="I100" t="n">
-        <v>39.1</v>
+        <v>52.4</v>
       </c>
       <c r="J100" t="n">
-        <v>26.1</v>
+        <v>30.2</v>
       </c>
       <c r="K100" t="n">
-        <v>0.85</v>
+        <v>0.65</v>
       </c>
       <c r="L100" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
     </row>
     <row r="101">
@@ -5052,16 +5052,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Maidstone Utd</t>
+          <t>Eastleigh</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Enfield Town</t>
+          <t>Truro City</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5072,42 +5072,42 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>57.1</v>
+        <v>31.7</v>
       </c>
       <c r="H101" t="n">
-        <v>22.9</v>
+        <v>15.9</v>
       </c>
       <c r="I101" t="n">
-        <v>20</v>
+        <v>52.4</v>
       </c>
       <c r="J101" t="n">
-        <v>37.1</v>
+        <v>30.2</v>
       </c>
       <c r="K101" t="n">
-        <v>0.83</v>
+        <v>0.65</v>
       </c>
       <c r="L101" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Al-Raed</t>
+          <t>FK Sarajevo</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Al Jubail</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5118,42 +5118,42 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>66.7</v>
+        <v>34.5</v>
       </c>
       <c r="H102" t="n">
-        <v>33.3</v>
+        <v>32.7</v>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>32.7</v>
       </c>
       <c r="J102" t="n">
-        <v>28.2</v>
+        <v>67.3</v>
       </c>
       <c r="K102" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="L102" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5164,42 +5164,42 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>50</v>
+        <v>34.5</v>
       </c>
       <c r="H103" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="I103" t="n">
-        <v>15.8</v>
+        <v>32.7</v>
       </c>
       <c r="J103" t="n">
-        <v>68.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K103" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L103" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wigan Athletic U21</t>
+          <t>Gateshead</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Fleetwood Town U21</t>
+          <t>Morecambe</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5210,42 +5210,42 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>50</v>
+        <v>27.1</v>
       </c>
       <c r="H104" t="n">
-        <v>34.2</v>
+        <v>23.4</v>
       </c>
       <c r="I104" t="n">
-        <v>15.8</v>
+        <v>49.5</v>
       </c>
       <c r="J104" t="n">
-        <v>68.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K104" t="n">
-        <v>0.82</v>
+        <v>0.64</v>
       </c>
       <c r="L104" t="n">
-        <v>38</v>
+        <v>107</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lucko</t>
+          <t>Hertha Zehlendorf</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Trnje</t>
+          <t>BSG Chemie Leipzig</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.6</v>
+        <v>2.39</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5256,42 +5256,42 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>48.9</v>
+        <v>27.1</v>
       </c>
       <c r="H105" t="n">
-        <v>34</v>
+        <v>23.4</v>
       </c>
       <c r="I105" t="n">
-        <v>17</v>
+        <v>49.5</v>
       </c>
       <c r="J105" t="n">
-        <v>55.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K105" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="L105" t="n">
-        <v>47</v>
+        <v>107</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Buxton</t>
+          <t>Fortaleza EC</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>King's Lynn Town</t>
+          <t>Maguary PE</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1.97</v>
+        <v>1.26</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5302,42 +5302,42 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="H106" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="I106" t="n">
-        <v>26.2</v>
+        <v>17.4</v>
       </c>
       <c r="J106" t="n">
-        <v>47.6</v>
+        <v>37</v>
       </c>
       <c r="K106" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="L106" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Al Bukayriyah</t>
+          <t>Breidablik</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Al Jandal</t>
+          <t>Leiknir R.</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5348,42 +5348,42 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>40.5</v>
+        <v>50</v>
       </c>
       <c r="H107" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="I107" t="n">
-        <v>26.2</v>
+        <v>17.4</v>
       </c>
       <c r="J107" t="n">
-        <v>47.6</v>
+        <v>37</v>
       </c>
       <c r="K107" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="L107" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2.36</v>
+        <v>1.25</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5394,42 +5394,42 @@
         <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>32.7</v>
+        <v>50</v>
       </c>
       <c r="H108" t="n">
-        <v>22.4</v>
+        <v>32.6</v>
       </c>
       <c r="I108" t="n">
-        <v>44.9</v>
+        <v>17.4</v>
       </c>
       <c r="J108" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K108" t="n">
-        <v>0.77</v>
+        <v>0.62</v>
       </c>
       <c r="L108" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>22:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Paris Saint Germain</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Instituto Cordoba</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5440,42 +5440,42 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="H109" t="n">
-        <v>27.5</v>
+        <v>32.6</v>
       </c>
       <c r="I109" t="n">
-        <v>39.1</v>
+        <v>17.4</v>
       </c>
       <c r="J109" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="K109" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="L109" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Abha</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Al Anwar</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5486,42 +5486,42 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>54.8</v>
+        <v>39.5</v>
       </c>
       <c r="H110" t="n">
-        <v>32.3</v>
+        <v>39.5</v>
       </c>
       <c r="I110" t="n">
-        <v>12.9</v>
+        <v>20.9</v>
       </c>
       <c r="J110" t="n">
-        <v>45.2</v>
+        <v>62.8</v>
       </c>
       <c r="K110" t="n">
-        <v>0.74</v>
+        <v>0.61</v>
       </c>
       <c r="L110" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Gainsborough Trinity</t>
+          <t>Taubaté</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Leek Town</t>
+          <t>XV de Piracicaba</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1.61</v>
+        <v>2.84</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5532,42 +5532,42 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>44.4</v>
+        <v>19</v>
       </c>
       <c r="H111" t="n">
-        <v>20</v>
+        <v>28.6</v>
       </c>
       <c r="I111" t="n">
-        <v>35.6</v>
+        <v>52.4</v>
       </c>
       <c r="J111" t="n">
-        <v>40</v>
+        <v>28.6</v>
       </c>
       <c r="K111" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="L111" t="n">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Escobedo</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>2.42</v>
+        <v>2.82</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5578,42 +5578,42 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="H112" t="n">
-        <v>30</v>
+        <v>28.6</v>
       </c>
       <c r="I112" t="n">
-        <v>40</v>
+        <v>52.4</v>
       </c>
       <c r="J112" t="n">
-        <v>66</v>
+        <v>28.6</v>
       </c>
       <c r="K112" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="L112" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Estrela U23</t>
+          <t>Al-Shabab</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Estoril U23</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>2.41</v>
+        <v>2.92</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5624,42 +5624,42 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>28.9</v>
+        <v>13.3</v>
       </c>
       <c r="H113" t="n">
-        <v>39.5</v>
+        <v>30</v>
       </c>
       <c r="I113" t="n">
-        <v>31.6</v>
+        <v>56.7</v>
       </c>
       <c r="J113" t="n">
-        <v>63.2</v>
+        <v>30</v>
       </c>
       <c r="K113" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="L113" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Kettering Town</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AFC Sudbury</t>
+          <t>Vitoria</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -5670,42 +5670,42 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>51.4</v>
+        <v>16.7</v>
       </c>
       <c r="H114" t="n">
-        <v>35.1</v>
+        <v>16.7</v>
       </c>
       <c r="I114" t="n">
-        <v>13.5</v>
+        <v>66.7</v>
       </c>
       <c r="J114" t="n">
-        <v>54.1</v>
+        <v>33.3</v>
       </c>
       <c r="K114" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="L114" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Doncaster</t>
+          <t>Criciuma U20</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Luton</t>
+          <t>Cruzeiro U20</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2.54</v>
+        <v>2.93</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -5716,42 +5716,42 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>26.7</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>11.1</v>
+        <v>36.4</v>
       </c>
       <c r="I115" t="n">
-        <v>62.2</v>
+        <v>63.6</v>
       </c>
       <c r="J115" t="n">
-        <v>24.4</v>
+        <v>63.6</v>
       </c>
       <c r="K115" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Blackburn</t>
+          <t>Detonit Plachkovica</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.45</v>
+        <v>13.25</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -5762,42 +5762,42 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>39.6</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Hungerford Town</t>
+          <t>Jeddah Club</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bracknell Town</t>
+          <t>Al Diriyah</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.44</v>
+        <v>8.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -5808,42 +5808,42 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>39.6</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>0.66</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Palmeiras U20</t>
+          <t>ES Metlaoui</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>São Paulo U20</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1.84</v>
+        <v>7.7</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -5854,22 +5854,22 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>34.5</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="J118" t="n">
-        <v>67.3</v>
+        <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L118" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -5880,16 +5880,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>United of Manchester</t>
+          <t>Ruthin Town</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Stockton Town</t>
+          <t>Airbus UK</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2.32</v>
+        <v>10</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -5900,527 +5900,21 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>27.1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>66.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
-        <v>0.64</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Al Khaleej Saihat</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Al Kholood</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H120" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="I120" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J120" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L120" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Olympiakos Piraeus</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" t="n">
-        <v>0</v>
-      </c>
-      <c r="G121" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H121" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="I121" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J121" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="K121" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L121" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Ceramica Cleopatra</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ismaily SC</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="n">
-        <v>0</v>
-      </c>
-      <c r="G122" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="H122" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="I122" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="J122" t="n">
-        <v>53.8</v>
-      </c>
-      <c r="K122" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="L122" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Wrexham</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Portsmouth</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" t="n">
-        <v>0</v>
-      </c>
-      <c r="G123" t="n">
-        <v>30</v>
-      </c>
-      <c r="H123" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="I123" t="n">
-        <v>43.3</v>
-      </c>
-      <c r="J123" t="n">
-        <v>60</v>
-      </c>
-      <c r="K123" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L123" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Dumbarton</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Clyde</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="n">
-        <v>0</v>
-      </c>
-      <c r="G124" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H124" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="I124" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="J124" t="n">
-        <v>50</v>
-      </c>
-      <c r="K124" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="L124" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Alvechurch</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Real Bedford</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>0</v>
-      </c>
-      <c r="G125" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H125" t="n">
-        <v>30</v>
-      </c>
-      <c r="I125" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J125" t="n">
-        <v>30</v>
-      </c>
-      <c r="K125" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L125" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Ghazl El Mehalla</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Pyramids FC</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" t="n">
-        <v>0</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0</v>
-      </c>
-      <c r="J126" t="n">
-        <v>0</v>
-      </c>
-      <c r="K126" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Cardiff City U21</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Colchester United U21</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>0</v>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Al-Hazm</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Al-Ittihad FC</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Al Taawon</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Al-Hilal Saudi FC</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>0</v>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Thanh Hóa</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Công An Nhân Dân</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" t="n">
-        <v>0</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
         <v>0</v>
       </c>
     </row>

--- a/sports_data.xlsx
+++ b/sports_data.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,66 +413,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Home Team</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Away Team</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Home Odds</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>AI Recommendation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Hit rate</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Home Win %</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Draw %</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Away Win %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Over %</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Expected ROI</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Sample Count</t>
         </is>
@@ -493,21 +481,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PSM Makassar</t>
+          <t>FC Astana</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.97</v>
+        <v>4.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -527,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1.95</v>
+        <v>4.75</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -539,21 +527,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Buriram United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Khon Kaen United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.05</v>
+        <v>3.36</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -573,102 +561,102 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>54.5</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>1.05</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Castanhal</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Guarani Campinas</t>
+          <t>FK Neftekhimik</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3.7</v>
+        <v>1.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Al-Nassr</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.5</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>100</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -677,47 +665,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Barcelona B</t>
+          <t>North Texas</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>100</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -728,108 +716,108 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FC Winterthur</t>
+          <t>FK Zalgiris Vilnius</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FC Thun</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.25</v>
+        <v>1.63</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>100</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Santos U20</t>
+          <t>Kairat Almaty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Grêmio U20</t>
+          <t>Aktobe</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="H8" t="n">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
-        <v>0.85</v>
+        <v>1.55</v>
       </c>
       <c r="L8" t="n">
-        <v>81</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.47</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -837,183 +825,183 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>82.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>82.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>39.3</v>
+        <v>50</v>
       </c>
       <c r="K9" t="n">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="L9" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Barquereño</t>
+          <t>Al-Jazira</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tropezón</t>
+          <t>Khorfakkan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.95</v>
+        <v>1.32</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="L10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Boca Juniors</t>
+          <t>Club America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gimnasia Chivilcoy</t>
+          <t>Mazatlán</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
-        <v>0.79</v>
+        <v>1.25</v>
       </c>
       <c r="L11" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Birkirkara</t>
+          <t>Krasava Ypsonas</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pietà Hotspurs</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>78.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>68.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
-        <v>21.1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>78.90000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="L12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ciudad de Lucena</t>
+          <t>Junior</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chiclana</t>
+          <t>Fortaleza FC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1021,45 +1009,45 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>44.1</v>
+        <v>66.7</v>
       </c>
       <c r="H13" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>42.4</v>
+        <v>33.3</v>
       </c>
       <c r="J13" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>0.64</v>
+        <v>1.1</v>
       </c>
       <c r="L13" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Žilina U19</t>
+          <t>Manchester City U21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Club Brugge U19</t>
+          <t>Liverpool U21</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.15</v>
+        <v>1.61</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1067,45 +1055,45 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>44.4</v>
+        <v>66.7</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>55.6</v>
+        <v>33.3</v>
       </c>
       <c r="J14" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
       <c r="K14" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="L14" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>02:00</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Tigres UANL W</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Querétaro W</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1113,899 +1101,899 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>76.7</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>13.3</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>56.7</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.88</v>
+        <v>1.05</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sporting Cristal</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2 de Mayo</t>
+          <t>Atletico Tucuman</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1.48</v>
+        <v>2.75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>⚽ 2.5 Over</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>76.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>18.2</v>
+        <v>100</v>
       </c>
       <c r="J16" t="n">
-        <v>76.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Al Taee</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Al Arabi SC</t>
+          <t>Argentinos JRS</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Shirak</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>FC Noah</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.49</v>
+        <v>6.45</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="J18" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Villarreal U19</t>
+          <t>Chapecoense-sc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Legia Warszawa U19</t>
+          <t>Gremio</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1.44</v>
+        <v>2.77</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Silkeborg</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nacional AM</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.27</v>
+        <v>2.17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>74.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>74.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>9.300000000000001</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>16.3</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>60.5</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>43</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ypiranga-RS</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ji-Paraná</t>
+          <t>Estac Troyes</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.22</v>
+        <v>2.88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>74.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>74.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>16.3</v>
+        <v>100</v>
       </c>
       <c r="J21" t="n">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ulytau</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlético Alagoinhas</t>
+          <t>Kyzyl-Zhar</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.22</v>
+        <v>2.86</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>74.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>74.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>16.3</v>
+        <v>100</v>
       </c>
       <c r="J22" t="n">
-        <v>60.5</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
-        <v>0.93</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Independiente Medellin</t>
+          <t>FK Tobol Kostanay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Zhetysu</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>73.2</v>
+        <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>73.2</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>73.2</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Norwich</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Dravinja</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>72.2</v>
+        <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>72.2</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>72.2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Ventura County</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Real Jaén</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.6</v>
+        <v>3.32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>✈️ Away win</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>71.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I25" t="n">
-        <v>71.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>First Vienna W</t>
+          <t>Vancouver Whitecaps II</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Neulengbach W</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.47</v>
+        <v>2.81</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>🏠 Home Win</t>
+          <t>✈️ Away win</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>71.2</v>
+        <v>100</v>
       </c>
       <c r="G26" t="n">
-        <v>71.2</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>11.5</v>
+        <v>100</v>
       </c>
       <c r="J26" t="n">
-        <v>59.6</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Al-Faisaly FC</t>
+          <t>Rakhine United</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Al Ula</t>
+          <t>I.S.P.E</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.14</v>
+        <v>2.02</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>83.3</v>
       </c>
       <c r="G27" t="n">
-        <v>22.9</v>
+        <v>83.3</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>17.1</v>
+        <v>16.7</v>
       </c>
       <c r="J27" t="n">
-        <v>25.7</v>
+        <v>83.3</v>
       </c>
       <c r="K27" t="n">
-        <v>0.72</v>
+        <v>1.71</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al-Khabourah</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.45</v>
+        <v>2.07</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="G28" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="H28" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="J28" t="n">
-        <v>50</v>
+        <v>83.3</v>
       </c>
       <c r="K28" t="n">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Al-Wasl FC</t>
+          <t>Arda Kardzhali</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Dobrudzha</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3.26</v>
+        <v>1.64</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>46.2</v>
+        <v>80</v>
       </c>
       <c r="G29" t="n">
-        <v>23.1</v>
+        <v>80</v>
       </c>
       <c r="H29" t="n">
-        <v>46.2</v>
+        <v>20</v>
       </c>
       <c r="I29" t="n">
-        <v>30.8</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>38.5</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>0.75</v>
+        <v>1.32</v>
       </c>
       <c r="L29" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Farnborough</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chippenham Town</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>45.7</v>
+        <v>80</v>
       </c>
       <c r="G30" t="n">
-        <v>39.1</v>
+        <v>40</v>
       </c>
       <c r="H30" t="n">
-        <v>45.7</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>15.2</v>
+        <v>60</v>
       </c>
       <c r="J30" t="n">
-        <v>31.5</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RB Bragantino</t>
+          <t>Bulleen Lions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atletico Paranaense</t>
+          <t>Brunswick Juventus FC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>44.8</v>
+        <v>80</v>
       </c>
       <c r="G31" t="n">
-        <v>40.3</v>
+        <v>40</v>
       </c>
       <c r="H31" t="n">
-        <v>44.8</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>14.9</v>
+        <v>60</v>
       </c>
       <c r="J31" t="n">
-        <v>31.3</v>
+        <v>80</v>
       </c>
       <c r="K31" t="n">
-        <v>0.71</v>
+        <v>0.9</v>
       </c>
       <c r="L31" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>San Marcos de Arica</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.94</v>
+        <v>2.05</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>42.9</v>
+        <v>77.8</v>
       </c>
       <c r="G32" t="n">
-        <v>38.1</v>
+        <v>66.7</v>
       </c>
       <c r="H32" t="n">
-        <v>42.9</v>
+        <v>33.3</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>38.1</v>
+        <v>77.8</v>
       </c>
       <c r="K32" t="n">
-        <v>1.12</v>
+        <v>1.37</v>
       </c>
       <c r="L32" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ceilândia</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jacuipense</t>
+          <t>Artis</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.43</v>
+        <v>1.69</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="G33" t="n">
-        <v>26.5</v>
+        <v>75</v>
       </c>
       <c r="H33" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>32.5</v>
+        <v>25</v>
       </c>
       <c r="J33" t="n">
-        <v>65.09999999999999</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>0.65</v>
+        <v>1.24</v>
       </c>
       <c r="L33" t="n">
-        <v>83</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>San Martin S.J.</t>
+          <t>Vicenza Virtus</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Inter U23</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.21</v>
+        <v>1.64</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>40.6</v>
+        <v>75</v>
       </c>
       <c r="G34" t="n">
-        <v>15.6</v>
+        <v>75</v>
       </c>
       <c r="H34" t="n">
-        <v>40.6</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>43.8</v>
+        <v>25</v>
       </c>
       <c r="J34" t="n">
-        <v>78.09999999999999</v>
+        <v>50</v>
       </c>
       <c r="K34" t="n">
-        <v>0.35</v>
+        <v>1.24</v>
       </c>
       <c r="L34" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2016,982 +2004,982 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Braintree</t>
+          <t>Chelmsford City</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aldershot Town</t>
+          <t>Slough Town</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.75</v>
+        <v>1.53</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>🤝 Draw</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K35" t="n">
-        <v>0.75</v>
+        <v>1.16</v>
       </c>
       <c r="L35" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Noja</t>
+          <t>FC Botosani</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Vimenor</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.92</v>
+        <v>1.55</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G36" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>33.3</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K36" t="n">
-        <v>2.63</v>
+        <v>1.16</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Gimnasia M.</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Independiente</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.6</v>
+        <v>1.49</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G37" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H37" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K37" t="n">
-        <v>2.19</v>
+        <v>0.72</v>
       </c>
       <c r="L37" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Belgrano U20</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>Nacional U20</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>3.44</v>
+        <v>2.27</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G38" t="n">
-        <v>53.8</v>
+        <v>25</v>
       </c>
       <c r="H38" t="n">
-        <v>30.8</v>
+        <v>75</v>
       </c>
       <c r="I38" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Airdrie United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Wolves</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.76</v>
+        <v>1.57</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>⚽ 2.5 Over</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G39" t="n">
-        <v>64.09999999999999</v>
+        <v>25</v>
       </c>
       <c r="H39" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="I39" t="n">
-        <v>17.9</v>
+        <v>50</v>
       </c>
       <c r="J39" t="n">
-        <v>69.2</v>
+        <v>75</v>
       </c>
       <c r="K39" t="n">
-        <v>1.76</v>
+        <v>0.39</v>
       </c>
       <c r="L39" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>remo</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Jong PSV U21</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.05</v>
+        <v>1.79</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>53.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>30.8</v>
+        <v>28.6</v>
       </c>
       <c r="I40" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>53.8</v>
+        <v>28.6</v>
       </c>
       <c r="K40" t="n">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="L40" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lamphun Warrior</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bangkok United</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3.22</v>
+        <v>1.73</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>47.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>9.5</v>
+        <v>28.6</v>
       </c>
       <c r="I41" t="n">
-        <v>42.9</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="K41" t="n">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="L41" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nakhon Ratchasima FC</t>
+          <t>Colo Colo</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rayong FC</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.28</v>
+        <v>1.58</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🏠 Home Win</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>47.6</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>9.5</v>
+        <v>14.3</v>
       </c>
       <c r="I42" t="n">
-        <v>42.9</v>
+        <v>14.3</v>
       </c>
       <c r="J42" t="n">
         <v>42.9</v>
       </c>
       <c r="K42" t="n">
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="L42" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gimnasia L.P.</t>
+          <t>Union Santa Fe</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Boca Juniors</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G43" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1.52</v>
+        <v>0.98</v>
       </c>
       <c r="L43" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hartlepool</t>
+          <t>Spaeri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3.02</v>
+        <v>2.42</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="I44" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Laktaši</t>
+          <t>Jeunes Fauves</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Victoria United</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>57.6</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>18.2</v>
+        <v>60</v>
       </c>
       <c r="I45" t="n">
-        <v>24.2</v>
+        <v>40</v>
       </c>
       <c r="J45" t="n">
-        <v>39.4</v>
+        <v>20</v>
       </c>
       <c r="K45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Achuapa</t>
+          <t>Deportivo Muñiz</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Xelajú</t>
+          <t>Yupanqui</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G46" t="n">
         <v>50</v>
       </c>
       <c r="H46" t="n">
-        <v>34.6</v>
+        <v>50</v>
       </c>
       <c r="I46" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>42.3</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="L46" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sportivo Ameliano</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G47" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="H47" t="n">
-        <v>22.2</v>
+        <v>50</v>
       </c>
       <c r="I47" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>55.6</v>
+        <v>75</v>
       </c>
       <c r="K47" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="L47" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atletico Torque</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>3.34</v>
+        <v>2.26</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>35.7</v>
+        <v>16.7</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>64.3</v>
+        <v>33.3</v>
       </c>
       <c r="J48" t="n">
-        <v>57.1</v>
+        <v>66.7</v>
       </c>
       <c r="K48" t="n">
-        <v>1.2</v>
+        <v>0.38</v>
       </c>
       <c r="L48" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Yeovil Town</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sutton Utd</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G49" t="n">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>30.3</v>
+        <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>21.2</v>
+        <v>50</v>
       </c>
       <c r="J49" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Teruel</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.25</v>
+        <v>3.86</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
         <v>50</v>
       </c>
-      <c r="H50" t="n">
-        <v>18.4</v>
-      </c>
       <c r="I50" t="n">
-        <v>31.6</v>
+        <v>50</v>
       </c>
       <c r="J50" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="K50" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sao Bento</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Linense</t>
+          <t>Iğdır FK</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>5.6</v>
+        <v>50</v>
       </c>
       <c r="I51" t="n">
-        <v>61.1</v>
+        <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>61.1</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>AFC Bournemouth U21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Thor Akureyri</t>
+          <t>Barnsley U21</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>1.38</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G52" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="H52" t="n">
-        <v>22.2</v>
+        <v>40</v>
       </c>
       <c r="I52" t="n">
-        <v>44.4</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>55.6</v>
+        <v>60</v>
       </c>
       <c r="K52" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Oita Trinita</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Biwako Shiga</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1.53</v>
+        <v>2.57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G53" t="n">
-        <v>65.8</v>
+        <v>20</v>
       </c>
       <c r="H53" t="n">
-        <v>18.4</v>
+        <v>40</v>
       </c>
       <c r="I53" t="n">
-        <v>15.8</v>
+        <v>40</v>
       </c>
       <c r="J53" t="n">
-        <v>39.5</v>
+        <v>40</v>
       </c>
       <c r="K53" t="n">
-        <v>1.02</v>
+        <v>0.51</v>
       </c>
       <c r="L53" t="n">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ayutthaya FC</t>
+          <t>Monza U20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ratchaburi</t>
+          <t>Cesena U20</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.02</v>
+        <v>2.54</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G54" t="n">
-        <v>33.3</v>
+        <v>20</v>
       </c>
       <c r="H54" t="n">
-        <v>5.6</v>
+        <v>40</v>
       </c>
       <c r="I54" t="n">
-        <v>61.1</v>
+        <v>40</v>
       </c>
       <c r="J54" t="n">
-        <v>61.1</v>
+        <v>40</v>
       </c>
       <c r="K54" t="n">
-        <v>1.02</v>
+        <v>0.51</v>
       </c>
       <c r="L54" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Inter De Limeira</t>
+          <t>Estoril U23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Oeste</t>
+          <t>Farense U23</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.04</v>
+        <v>2.51</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G55" t="n">
-        <v>49.3</v>
+        <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="I55" t="n">
-        <v>35.2</v>
+        <v>40</v>
       </c>
       <c r="J55" t="n">
-        <v>50.7</v>
+        <v>40</v>
       </c>
       <c r="K55" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="L55" t="n">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.16</v>
+        <v>3.58</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3002,22 +2990,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>47.2</v>
+        <v>50</v>
       </c>
       <c r="H56" t="n">
-        <v>28.3</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>24.5</v>
+        <v>50</v>
       </c>
       <c r="J56" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="L56" t="n">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3028,16 +3016,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Al-Shabab</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3048,42 +3036,42 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="H57" t="n">
-        <v>32.5</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>32.5</v>
+        <v>50</v>
       </c>
       <c r="J57" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>1.58</v>
       </c>
       <c r="L57" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>América Mineiro U20</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fluminense U20</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3094,42 +3082,42 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>37.5</v>
+        <v>55.6</v>
       </c>
       <c r="H58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I58" t="n">
         <v>33.3</v>
       </c>
-      <c r="I58" t="n">
-        <v>29.2</v>
-      </c>
       <c r="J58" t="n">
-        <v>54.2</v>
+        <v>33.3</v>
       </c>
       <c r="K58" t="n">
-        <v>0.99</v>
+        <v>1.25</v>
       </c>
       <c r="L58" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Belgrano Cordoba</t>
+          <t>FC Porto B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atletico Tucuman</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.69</v>
+        <v>1.97</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3140,42 +3128,42 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>58.8</v>
+        <v>60</v>
       </c>
       <c r="H59" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>23.5</v>
+        <v>40</v>
       </c>
       <c r="J59" t="n">
-        <v>35.3</v>
+        <v>20</v>
       </c>
       <c r="K59" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="L59" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Çorum FK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chapecoense-sc</t>
+          <t>Esenler Erokspor</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3186,42 +3174,42 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>61.5</v>
+        <v>50</v>
       </c>
       <c r="H60" t="n">
-        <v>15.4</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>23.1</v>
+        <v>50</v>
       </c>
       <c r="J60" t="n">
         <v>50</v>
       </c>
       <c r="K60" t="n">
-        <v>0.95</v>
+        <v>1.17</v>
       </c>
       <c r="L60" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Al Wahda FC</t>
+          <t>Internacional Palmira</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ajman</t>
+          <t>Ind. Yumbo</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1.57</v>
+        <v>2.08</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3232,42 +3220,42 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>60.5</v>
+        <v>55.6</v>
       </c>
       <c r="H61" t="n">
-        <v>21.1</v>
+        <v>11.1</v>
       </c>
       <c r="I61" t="n">
-        <v>18.4</v>
+        <v>33.3</v>
       </c>
       <c r="J61" t="n">
-        <v>60.5</v>
+        <v>66.7</v>
       </c>
       <c r="K61" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="L61" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3278,42 +3266,42 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>45.6</v>
+        <v>55.6</v>
       </c>
       <c r="H62" t="n">
-        <v>17.5</v>
+        <v>11.1</v>
       </c>
       <c r="I62" t="n">
-        <v>36.8</v>
+        <v>33.3</v>
       </c>
       <c r="J62" t="n">
-        <v>35.1</v>
+        <v>66.7</v>
       </c>
       <c r="K62" t="n">
-        <v>0.93</v>
+        <v>1.14</v>
       </c>
       <c r="L62" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Birmingham</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2.48</v>
+        <v>3.25</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3324,42 +3312,42 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>37.5</v>
+        <v>33.3</v>
       </c>
       <c r="H63" t="n">
-        <v>17.9</v>
+        <v>33.3</v>
       </c>
       <c r="I63" t="n">
-        <v>44.6</v>
+        <v>33.3</v>
       </c>
       <c r="J63" t="n">
-        <v>37.5</v>
+        <v>66.7</v>
       </c>
       <c r="K63" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="L63" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sheffield Utd</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coventry</t>
+          <t>Defensa Y Justicia</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.42</v>
+        <v>2.16</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3370,42 +3358,42 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="H64" t="n">
-        <v>17.9</v>
+        <v>33.3</v>
       </c>
       <c r="I64" t="n">
-        <v>44.6</v>
+        <v>16.7</v>
       </c>
       <c r="J64" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="K64" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="L64" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gzira United</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Hibernians</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3416,42 +3404,42 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="H65" t="n">
-        <v>17.9</v>
+        <v>16.7</v>
       </c>
       <c r="I65" t="n">
-        <v>44.6</v>
+        <v>33.3</v>
       </c>
       <c r="J65" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.92</v>
+        <v>1.08</v>
       </c>
       <c r="L65" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Selaya</t>
+          <t>Cardiff MET</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Guarnizo</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3.36</v>
+        <v>2.15</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3462,42 +3450,42 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>27.3</v>
+        <v>50</v>
       </c>
       <c r="H66" t="n">
-        <v>36.4</v>
+        <v>16.7</v>
       </c>
       <c r="I66" t="n">
-        <v>36.4</v>
+        <v>33.3</v>
       </c>
       <c r="J66" t="n">
-        <v>45.5</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="L66" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Real Madrid U19</t>
+          <t>Roda</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chelsea U19</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3508,42 +3496,42 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>46.9</v>
+        <v>57.1</v>
       </c>
       <c r="H67" t="n">
-        <v>24.5</v>
+        <v>14.3</v>
       </c>
       <c r="I67" t="n">
         <v>28.6</v>
       </c>
       <c r="J67" t="n">
-        <v>36.7</v>
+        <v>57.1</v>
       </c>
       <c r="K67" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="L67" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>02:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Antigua GFC</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Guastatoya</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3554,42 +3542,42 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="H68" t="n">
-        <v>22.4</v>
+        <v>25</v>
       </c>
       <c r="I68" t="n">
-        <v>20.4</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>38.8</v>
+        <v>50</v>
       </c>
       <c r="K68" t="n">
-        <v>0.89</v>
+        <v>1.02</v>
       </c>
       <c r="L68" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Al Zulfi</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Al-Adalah</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3600,42 +3588,42 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>53.8</v>
+        <v>60</v>
       </c>
       <c r="H69" t="n">
-        <v>28.2</v>
+        <v>20</v>
       </c>
       <c r="I69" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>53.8</v>
+        <v>40</v>
       </c>
       <c r="K69" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
       <c r="L69" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Velez Sarsfield</t>
+          <t>Swansea City U21</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Sheffield Wednesday U21</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.82</v>
+        <v>1.48</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3646,42 +3634,42 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>47.7</v>
+        <v>66.7</v>
       </c>
       <c r="H70" t="n">
-        <v>27.9</v>
+        <v>16.7</v>
       </c>
       <c r="I70" t="n">
-        <v>24.4</v>
+        <v>16.7</v>
       </c>
       <c r="J70" t="n">
-        <v>38.4</v>
+        <v>66.7</v>
       </c>
       <c r="K70" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="L70" t="n">
-        <v>86</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AL Masry</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Future FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3692,42 +3680,42 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>41.1</v>
+        <v>50</v>
       </c>
       <c r="H71" t="n">
-        <v>35.7</v>
+        <v>33.3</v>
       </c>
       <c r="I71" t="n">
-        <v>23.2</v>
+        <v>16.7</v>
       </c>
       <c r="J71" t="n">
-        <v>46.4</v>
+        <v>16.7</v>
       </c>
       <c r="K71" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="L71" t="n">
-        <v>56</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Estudiantes de Rio Cuarto</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.83</v>
+        <v>1.41</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3738,42 +3726,42 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>47.7</v>
+        <v>60</v>
       </c>
       <c r="H72" t="n">
-        <v>27.9</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>24.4</v>
+        <v>40</v>
       </c>
       <c r="J72" t="n">
-        <v>38.4</v>
+        <v>60</v>
       </c>
       <c r="K72" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="L72" t="n">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Huddersfield Town U21</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hull City U21</t>
+          <t>CFR 1907 Cluj</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.83</v>
+        <v>2.51</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3784,22 +3772,22 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>47.7</v>
+        <v>33.3</v>
       </c>
       <c r="H73" t="n">
-        <v>27.9</v>
+        <v>33.3</v>
       </c>
       <c r="I73" t="n">
-        <v>24.4</v>
+        <v>33.3</v>
       </c>
       <c r="J73" t="n">
-        <v>38.4</v>
+        <v>33.3</v>
       </c>
       <c r="K73" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="L73" t="n">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -3810,16 +3798,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Newells Old Boys</t>
+          <t>Barranquilla</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Estudiantes L.P.</t>
+          <t>Bogota FC</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.28</v>
+        <v>2.24</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3830,42 +3818,42 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>26.7</v>
+        <v>37.5</v>
       </c>
       <c r="H74" t="n">
-        <v>26.7</v>
+        <v>25</v>
       </c>
       <c r="I74" t="n">
-        <v>46.7</v>
+        <v>37.5</v>
       </c>
       <c r="J74" t="n">
-        <v>20</v>
+        <v>37.5</v>
       </c>
       <c r="K74" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="L74" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Bodrum FK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Libertad Asuncion</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3876,42 +3864,42 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H75" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="I75" t="n">
-        <v>36.9</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>69.2</v>
+        <v>50</v>
       </c>
       <c r="K75" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="L75" t="n">
-        <v>65</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Leixões U23</t>
+          <t>Ararat-Armenia</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Academico Viseu U23</t>
+          <t>Van</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>2.82</v>
+        <v>1.32</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3922,42 +3910,42 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H76" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>40</v>
       </c>
       <c r="J76" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K76" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Flamengo</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3968,22 +3956,22 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="H77" t="n">
-        <v>22.9</v>
+        <v>16.7</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="J77" t="n">
-        <v>37.1</v>
+        <v>66.7</v>
       </c>
       <c r="K77" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="L77" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78">
@@ -3994,16 +3982,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Al-Fayha</t>
+          <t>Jong AZ</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NEOM</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4014,42 +4002,42 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>31.2</v>
+        <v>50</v>
       </c>
       <c r="H78" t="n">
-        <v>37.5</v>
+        <v>16.7</v>
       </c>
       <c r="I78" t="n">
-        <v>31.2</v>
+        <v>33.3</v>
       </c>
       <c r="J78" t="n">
-        <v>43.8</v>
+        <v>66.7</v>
       </c>
       <c r="K78" t="n">
-        <v>0.83</v>
+        <v>0.78</v>
       </c>
       <c r="L78" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Zeljeznicar Sarajevo</t>
+          <t>Leeds United U21</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Tottenham Hotspur U21</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.56</v>
+        <v>3.76</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4060,42 +4048,42 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>52.9</v>
+        <v>20</v>
       </c>
       <c r="H79" t="n">
-        <v>29.4</v>
+        <v>20</v>
       </c>
       <c r="I79" t="n">
-        <v>17.6</v>
+        <v>60</v>
       </c>
       <c r="J79" t="n">
-        <v>58.8</v>
+        <v>40</v>
       </c>
       <c r="K79" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="L79" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Monte Azul</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4106,22 +4094,22 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>30.8</v>
+        <v>28.6</v>
       </c>
       <c r="H80" t="n">
-        <v>34.6</v>
+        <v>14.3</v>
       </c>
       <c r="I80" t="n">
-        <v>34.6</v>
+        <v>57.1</v>
       </c>
       <c r="J80" t="n">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="K80" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="L80" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -4132,16 +4120,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SG Sonnenhof Grossaspach</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Freiburg II</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.52</v>
+        <v>2.35</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4152,42 +4140,42 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>52.9</v>
+        <v>28.6</v>
       </c>
       <c r="H81" t="n">
-        <v>29.4</v>
+        <v>14.3</v>
       </c>
       <c r="I81" t="n">
-        <v>17.6</v>
+        <v>57.1</v>
       </c>
       <c r="J81" t="n">
-        <v>58.8</v>
+        <v>42.9</v>
       </c>
       <c r="K81" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="L81" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>AEK Larnaca</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.22</v>
+        <v>5.85</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4198,42 +4186,42 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>65.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>15.6</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>18.8</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>59.4</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Burnley U21</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Brighton U21</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4244,42 +4232,42 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>52.9</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>17.6</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Benfica U19</t>
+          <t>Meshakhte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AZ U19</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.51</v>
+        <v>2.71</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4290,42 +4278,42 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>52.6</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>24.6</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>57.9</v>
+        <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.82</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Woking</t>
+          <t>Mezokovesd-zsory</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Solihull Moors</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.21</v>
+        <v>4.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4336,42 +4324,42 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Águilas</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Recreativo Huelva</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>2.23</v>
+        <v>2.47</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4382,42 +4370,42 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sevilla Atletico</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1.64</v>
+        <v>3.96</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4428,42 +4416,42 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Santo André</t>
+          <t>Sassuolo W</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sertãozinho</t>
+          <t>Inter Milano W</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.9</v>
+        <v>5.7</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4474,42 +4462,42 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>39.3</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>46.4</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>2.3</v>
+        <v>2.92</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4520,42 +4508,42 @@
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Al Nasar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prachuap</t>
+          <t>Al Kuwait</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.33</v>
+        <v>6.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4566,42 +4554,42 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>22.4</v>
+        <v>0</v>
       </c>
       <c r="I90" t="n">
-        <v>44.9</v>
+        <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Al Tadhamon</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Cianorte</t>
+          <t>Al Qadsia</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.22</v>
+        <v>5.95</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4612,42 +4600,42 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>39.1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Béchar Djedid</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MC Saida</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4658,42 +4646,42 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>America-RN</t>
+          <t>Tanjong Pagar</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>GAS</t>
+          <t>Tampines Rovers</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.14</v>
+        <v>14.25</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4704,42 +4692,42 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>61.9</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I93" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sporting Braga U23</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Torreense U23</t>
+          <t>Las Palmas</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>2.81</v>
+        <v>2.91</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -4750,42 +4738,42 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PSG U19</t>
+          <t>Şanlıurfaspor</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HJK U19</t>
+          <t>Altınordu</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.12</v>
+        <v>1.31</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -4796,42 +4784,42 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>61.9</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Karaman Belediyespor</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Votuporanguense</t>
+          <t>Batman Petrolspor</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.69</v>
+        <v>24</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -4842,42 +4830,42 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>41.1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>27.4</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>31.6</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.68</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Taunton Town</t>
+          <t>Kastamonuspor 1966</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wimborne Town</t>
+          <t>Beyoğlu Yeni Çarşı</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -4888,42 +4876,42 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>15.7</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
-        <v>56.9</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>58.8</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Dibba Al-Fujairah</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.32</v>
+        <v>13.75</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -4934,987 +4922,21 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>28.6</v>
+        <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>54.3</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>45.7</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>São Luiz</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Maranhão</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>0</v>
-      </c>
-      <c r="G99" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="H99" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I99" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J99" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K99" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L99" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Água Santa</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Grêmio Prudente</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>0</v>
-      </c>
-      <c r="G100" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="H100" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I100" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J100" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L100" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Eastleigh</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Truro City</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="H101" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="I101" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J101" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="L101" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>FK Sarajevo</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Velež</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H102" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="I102" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J102" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L102" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Cruzeiro</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Corinthians</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="H103" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="I103" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="J103" t="n">
-        <v>67.3</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L103" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Gateshead</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Morecambe</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H104" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I104" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J104" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L104" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Hertha Zehlendorf</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>BSG Chemie Leipzig</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="H105" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="I105" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="J105" t="n">
-        <v>66.40000000000001</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L105" t="n">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>00:30</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Fortaleza EC</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Maguary PE</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" t="n">
-        <v>50</v>
-      </c>
-      <c r="H106" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I106" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J106" t="n">
-        <v>37</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L106" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Breidablik</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Leiknir R.</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>0</v>
-      </c>
-      <c r="G107" t="n">
-        <v>50</v>
-      </c>
-      <c r="H107" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I107" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J107" t="n">
-        <v>37</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L107" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Bahia</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>O'Higgins</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>0</v>
-      </c>
-      <c r="G108" t="n">
-        <v>50</v>
-      </c>
-      <c r="H108" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I108" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J108" t="n">
-        <v>37</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L108" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Paris Saint Germain</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>50</v>
-      </c>
-      <c r="H109" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="I109" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="J109" t="n">
-        <v>37</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L109" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>National Bank of Egypt</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Pharco</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="H110" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="I110" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="J110" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="L110" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Taubaté</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>XV de Piracicaba</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>19</v>
-      </c>
-      <c r="H111" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I111" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J111" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K111" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L111" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Castro</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Escobedo</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" t="n">
-        <v>0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>19</v>
-      </c>
-      <c r="H112" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="I112" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J112" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="K112" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="L112" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Al-Shabab</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Al-Nahda</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H113" t="n">
-        <v>30</v>
-      </c>
-      <c r="I113" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="J113" t="n">
-        <v>30</v>
-      </c>
-      <c r="K113" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="L113" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Botafogo</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Vitoria</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="H114" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="I114" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="J114" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="L114" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Criciuma U20</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Cruzeiro U20</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="n">
-        <v>0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="I115" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="J115" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Detonit Plachkovica</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Sileks</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F116" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>18:45</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Jeddah Club</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Al Diriyah</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="n">
-        <v>0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>ES Metlaoui</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>ES Tunis</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="n">
-        <v>0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="n">
-        <v>0</v>
-      </c>
-      <c r="L118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Ruthin Town</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Airbus UK</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" t="n">
-        <v>0</v>
-      </c>
-      <c r="J119" t="n">
-        <v>0</v>
-      </c>
-      <c r="K119" t="n">
-        <v>0</v>
-      </c>
-      <c r="L119" t="n">
         <v>0</v>
       </c>
     </row>

--- a/sports_data.xlsx
+++ b/sports_data.xlsx
@@ -1323,7 +1323,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2551,21 +2551,21 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Envigado</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Real Cartagena</t>
+          <t>CFR 1907 Cluj</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2585,33 +2585,33 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="K47" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="L47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Liverpool Montevideo</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atletico Torque</t>
+          <t>Real Cartagena</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2622,42 +2622,42 @@
         <v>50</v>
       </c>
       <c r="G48" t="n">
-        <v>16.7</v>
+        <v>50</v>
       </c>
       <c r="H48" t="n">
         <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>66.7</v>
+        <v>75</v>
       </c>
       <c r="K48" t="n">
-        <v>0.38</v>
+        <v>1.12</v>
       </c>
       <c r="L48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Liverpool Montevideo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atletico Torque</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2668,42 +2668,42 @@
         <v>50</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>16.7</v>
       </c>
       <c r="H49" t="n">
         <v>50</v>
       </c>
       <c r="I49" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="J49" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3.86</v>
+        <v>2.6</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>50</v>
       </c>
       <c r="J50" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -2735,21 +2735,21 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iğdır FK</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.68</v>
+        <v>3.86</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>50</v>
       </c>
       <c r="J51" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -2781,21 +2781,21 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AFC Bournemouth U21</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Barnsley U21</t>
+          <t>Iğdır FK</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2803,45 +2803,45 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G52" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J52" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>AFC Bournemouth U21</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Barnsley U21</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.57</v>
+        <v>1.38</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2852,19 +2852,19 @@
         <v>40</v>
       </c>
       <c r="G53" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H53" t="n">
         <v>40</v>
       </c>
       <c r="I53" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="K53" t="n">
-        <v>0.51</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L53" t="n">
         <v>5</v>
@@ -2873,21 +2873,21 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Monza U20</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cesena U20</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2919,21 +2919,21 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Estoril U23</t>
+          <t>Monza U20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Farense U23</t>
+          <t>Cesena U20</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2965,67 +2965,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Estoril U23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Farense U23</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3.58</v>
+        <v>2.51</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>🤝 Draw</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I56" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K56" t="n">
-        <v>1.78</v>
+        <v>0.51</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Al-Shabab</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.1</v>
+        <v>3.58</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="L57" t="n">
         <v>2</v>
@@ -3057,21 +3057,21 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Al-Shabab</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3082,42 +3082,42 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J58" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="L58" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FC Porto B</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Oliveirense</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3128,42 +3128,42 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>60</v>
+        <v>55.6</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>11.1</v>
       </c>
       <c r="I59" t="n">
-        <v>40</v>
+        <v>33.3</v>
       </c>
       <c r="J59" t="n">
-        <v>20</v>
+        <v>33.3</v>
       </c>
       <c r="K59" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="L59" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Çorum FK</t>
+          <t>FC Porto B</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Esenler Erokspor</t>
+          <t>Oliveirense</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3174,42 +3174,42 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J60" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K60" t="n">
         <v>1.17</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>23:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Internacional Palmira</t>
+          <t>Çorum FK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ind. Yumbo</t>
+          <t>Esenler Erokspor</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3220,42 +3220,42 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="H61" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>33.3</v>
+        <v>50</v>
       </c>
       <c r="J61" t="n">
-        <v>66.7</v>
+        <v>50</v>
       </c>
       <c r="K61" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Danubio</t>
+          <t>Internacional Palmira</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Juventud</t>
+          <t>Ind. Yumbo</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3287,21 +3287,21 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Danubio</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Huracan</t>
+          <t>Juventud</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>33.3</v>
+        <v>55.6</v>
       </c>
       <c r="H63" t="n">
-        <v>33.3</v>
+        <v>11.1</v>
       </c>
       <c r="I63" t="n">
         <v>33.3</v>
@@ -3324,30 +3324,30 @@
         <v>66.7</v>
       </c>
       <c r="K63" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="L63" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Defensa Y Justicia</t>
+          <t>Huracan</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2.16</v>
+        <v>3.25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3358,42 +3358,42 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>50</v>
+        <v>33.3</v>
       </c>
       <c r="H64" t="n">
         <v>33.3</v>
       </c>
       <c r="I64" t="n">
-        <v>16.7</v>
+        <v>33.3</v>
       </c>
       <c r="J64" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="K64" t="n">
         <v>1.08</v>
       </c>
       <c r="L64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Derby</t>
+          <t>Defensa Y Justicia</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3407,13 +3407,13 @@
         <v>50</v>
       </c>
       <c r="H65" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="I65" t="n">
         <v>16.7</v>
       </c>
-      <c r="I65" t="n">
-        <v>33.3</v>
-      </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K65" t="n">
         <v>1.08</v>
@@ -3425,17 +3425,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Cardiff MET</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Derby</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -3471,21 +3471,21 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Roda</t>
+          <t>Cardiff MET</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3496,42 +3496,42 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>57.1</v>
+        <v>50</v>
       </c>
       <c r="H67" t="n">
-        <v>14.3</v>
+        <v>16.7</v>
       </c>
       <c r="I67" t="n">
-        <v>28.6</v>
+        <v>33.3</v>
       </c>
       <c r="J67" t="n">
-        <v>57.1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="L67" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pogon Szczecin</t>
+          <t>Roda</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Korona Kielce</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3542,42 +3542,42 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>14.3</v>
       </c>
       <c r="I68" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="J68" t="n">
-        <v>50</v>
+        <v>57.1</v>
       </c>
       <c r="K68" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="L68" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Irtysh</t>
+          <t>Pogon Szczecin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Korona Kielce</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3588,42 +3588,42 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H69" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K69" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="L69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Swansea City U21</t>
+          <t>Irtysh</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday U21</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3634,42 +3634,42 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>66.7</v>
+        <v>60</v>
       </c>
       <c r="H70" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="I70" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>66.7</v>
+        <v>40</v>
       </c>
       <c r="K70" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="L70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Torreense</t>
+          <t>Swansea City U21</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sheffield Wednesday U21</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3680,19 +3680,19 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>50</v>
+        <v>66.7</v>
       </c>
       <c r="H71" t="n">
-        <v>33.3</v>
+        <v>16.7</v>
       </c>
       <c r="I71" t="n">
         <v>16.7</v>
       </c>
       <c r="J71" t="n">
-        <v>16.7</v>
+        <v>66.7</v>
       </c>
       <c r="K71" t="n">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="L71" t="n">
         <v>6</v>
@@ -3701,21 +3701,21 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>Torreense</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Estudiantes de Rio Cuarto</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.41</v>
+        <v>1.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3726,42 +3726,42 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I72" t="n">
-        <v>40</v>
+        <v>16.7</v>
       </c>
       <c r="J72" t="n">
-        <v>60</v>
+        <v>16.7</v>
       </c>
       <c r="K72" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CFR 1907 Cluj</t>
+          <t>Estudiantes de Rio Cuarto</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.51</v>
+        <v>1.41</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3772,22 +3772,22 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="H73" t="n">
-        <v>33.3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
       <c r="J73" t="n">
-        <v>33.3</v>
+        <v>60</v>
       </c>
       <c r="K73" t="n">
-        <v>0.85</v>
+        <v>0.87</v>
       </c>
       <c r="L73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
